--- a/data_extactor/batch_10_fa/batch_0013_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0013_fa.xlsx
@@ -503,7 +503,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>AJAX | نرم‌افزار مدیریت دسترسی | نرم‌افزار اکتیو دایرکتوری | Adexa eGPS Suite | Adobe Acrobat | Adobe ActionScript | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | نرم‌افزار نصب خودکار | Bash | Berkeley Internet Domain Name BIND | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | پروتکل مسیریابی مرزی BGP | C | C# | C++ | Chef | Cisco Systems CiscoWorks | Cisco Webex | Citrix XenApp | نرم‌افزار رایانش ابری Citrix | مفسرهای فرمان | زبان مشترک تجاری COBOL | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار تشخیص خطای سیستم کامپیوتری | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | Dassault Systemes CATIA | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار رسم نمودار | Django | Docker | سیستم نام دامنه DNS | Drupal | پروتکل پیکربندی پویای میزبان DHCP | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار مدیریت عناصر | نرم‌افزار رمزنگاری | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی EAI | Epic Systems | Ethereal | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار فایروال | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Sites | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hewlett-Packard HP Network Node Manager | Hibernate ORM | Honeypot | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Director | IBM Domino | IBM InfoSphere DataStage | IBM NetView | IBM Notes | نرم‌افزار IBM Power Systems | نرم‌افزار IBM Tivoli | IBM WebSphere | نرم‌افزار محیط توسعه یکپارچه IDE | سیستم پیشگیری از نفوذ IPS | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | Lavalys Everest | Linux | LogMatrix NerveCenter | Mac HelpMate | نرم‌افزار پایگاه اطلاعات مدیریت MIB | Marketo Marketing Automation | McAfee | MicroStrategy | Micromuse NetCool | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Windows Sysprep | Microsoft Windows Terminal Services Access Manager | MongoDB | Moodle | نرم‌افزار نمودار ترافیک چند روتر MRTG | MySQL | Nagios | NetSuite ERP | نرم‌افزار مدیریت آدرس شبکه | نرم‌افزار ذخیره‌سازی متصل به شبکه NAS | نرم‌افزار تست عملکرد و بارگذاری شبکه و برنامه | نرم‌افزار تحلیل عملکرد شبکه و قطعات | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار نظارت بر در دسترس بودن شبکه | نرم‌افزار مستندسازی شبکه | نرم‌افزار تشخیص نفوذ به شبکه | سیستم‌های پیشگیری از نفوذ به شبکه NIPS | نرم‌افزار مدیریت شبکه | نرم‌افزار مدل‌سازی، نقشه‌برداری و تحلیل شبکه | نرم‌افزار خاموش کردن شبکه | نرم‌افزار نظارت و تحلیل جریان ترافیک شبکه | نرم‌افزار کاوشگر ترافیک شبکه | نرم‌افزار بهینه‌سازی شبکه، سرور و سیستم‌عامل | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Novell NetWare Management Station | نرم‌افزار محاسبه ترافیک آنلاین | پروتکل‌های مسیریابی متن‌باز OSPF | OpenService Open NerveCenter | نرم‌افزار کنترل فرآیند سیستم‌عامل | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Net Manager | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | نرم‌افزار فیلتر بسته | نرم‌افزار ردیابی بسته | ParentSquare | نرم‌افزار مدیریت رمز عبور | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار Perforce Helix | Perl | Ping Identity | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest BigBrother | Quest Erwin Data Modeler | Quest Foglight | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار کنترل دسکتاپ از راه دور | نرم‌افزار نظارت از راه دور | نرم‌افزار مدیریت نیازمندی‌ها | نرم‌افزار تحلیل ریشه خطا | نرم‌افزار تشخیص روت‌کیت | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | نرم‌افزار پوسته امن SSH | نرم‌افزار مدیریت حوادث امنیتی | ServiceNow | شل اسکریپت | نرم‌افزار پروتکل آسان مدیریت شبکه SNMP | Skype | Snort | SolarWinds | Splunk Enterprise | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Ghost Solution Suite | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار مهاجرت سیستم‌ها و برنامه‌ها | نرم‌افزار یکپارچه‌سازی سیستم‌ها | نرم‌افزار TKSoftware RCM | Tableau | Tcpdump | Teradata Database | Transact-SQL | UNIX | UNIX Shell | Ubuntu | VMware | Veritas NetBackup | نرم‌افزار مدیریت شبکه محلی مجازی | نرم‌افزار محاسبات شبکه مجازی VNC | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Wireshark | Zabbix | jQuery</t>
+          <t>AJAX | نرم‌افزار مدیریت دسترسی | نرم‌افزار اکتیو دایرکتوری | Adexa eGPS Suite | Adobe Acrobat | Adobe ActionScript | Adobe Dreamweaver | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple macOS | نرم‌افزار مدیریت برنامه‌ها | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | نرم‌افزار نصب خودکار | Bash | Berkeley Internet Domain Name BIND | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | پروتکل مسیریابی مرزی BGP | C | C# | C++ | Chef | Cisco Systems CiscoWorks | Cisco Webex | Citrix XenApp | نرم‌افزار رایانش ابری Citrix | مفسرهای فرمان | زبان مشترک تجاری COBOL | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار تشخیص خطای سیستم کامپیوتری | سیستم کنترل اطلاعات مشتری CICS | Dartware InterMapper | Dassault Systemes CATIA | نرم‌افزار پایگاه داده | Delphi Technology | نرم‌افزار نمودارکشی | Django | Docker | سیستم نام دامنه DNS | Drupal | پروتکل پیکربندی پویای میزبان DHCP | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | نرم‌افزار مدیریت عناصر | نرم‌افزار رمزگذاری | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Epic Systems | Ethereal | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | FileMaker Pro | نرم‌افزار فایروال | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Sites | نرم‌افزار میز کمک | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hewlett-Packard HP Network Node Manager | Hibernate ORM | هانی‌پات | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Director | IBM Domino | IBM InfoSphere DataStage | IBM NetView | IBM Notes | نرم‌افزار IBM Power Systems | نرم‌افزار IBM Tivoli | IBM WebSphere | نرم‌افزار محیط توسعه یکپارچه IDE | سیستم پیشگیری از نفوذ IPS | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | Lavalys Everest | Linux | LogMatrix NerveCenter | Mac HelpMate | نرم‌افزار پایگاه اطلاعات مدیریت MIB | Marketo Marketing Automation | McAfee | MicroStrategy | Micromuse NetCool | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft Excel | Microsoft Exchange | نرم‌افزار Microsoft Office | Microsoft Outlook | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Windows Sysprep | Microsoft Windows Terminal Services Access Manager | MongoDB | Moodle | نرم‌افزار ترسیم گراف ترافیک چند روتری MRTG | MySQL | Nagios | NetSuite ERP | نرم‌افزار مدیریت آدرس شبکه | نرم‌افزار ذخیره‌سازی متصل به شبکه NAS | نرم‌افزار تست بار و عملکرد شبکه و برنامه | نرم‌افزار تحلیل عملکرد شبکه و قطعات | نرم‌افزار ارزیابی آسیب‌پذیری شبکه و سیستم | نرم‌افزار نظارت بر در دسترس بودن شبکه | نرم‌افزار مستندسازی شبکه | نرم‌افزار تشخیص نفوذ شبکه | سیستم‌های پیشگیری از نفوذ شبکه NIPS | نرم‌افزار مدیریت شبکه | نرم‌افزار مدل‌سازی، نقشه‌برداری و تحلیل شبکه | نرم‌افزار خاموش کردن شبکه | نرم‌افزار نظارت و تحلیل جریان ترافیک شبکه | نرم‌افزار پروب ترافیک شبکه | نرم‌افزار بهینه‌سازی شبکه، سرور و سیستم عامل | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Novell NetWare Management Station | نرم‌افزار محاسبه‌گر ترافیک آنلاین | پروتکل‌های مسیریابی متن‌باز OSPF | OpenService Open NerveCenter | نرم‌افزار کنترل فرآیند سیستم‌عامل | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Net Manager | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle Taleo | Oracle WebLogic Server | PHP | نرم‌افزار فیلتر بسته | نرم‌افزار ردیابی بسته | ParentSquare | نرم‌افزار مدیریت پسورد | نرم‌افزار مدیریت وصله و به‌روزرسانی | نرم‌افزار Perforce Helix | Perl | Ping Identity | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest BigBrother | Quest Erwin Data Modeler | Quest Foglight | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار کنترل دسکتاپ از راه دور | نرم‌افزار نظارت از راه دور | نرم‌افزار مدیریت الزامات | نرم‌افزار تحلیل علت ریشه‌ای | نرم‌افزار شناسایی روت‌کیت | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | نرم‌افزار پوسته امن SSH | نرم‌افزار مدیریت حوادث امنیتی | ServiceNow | Shell script | نرم‌افزار پروتکل آسان مدیریت شبکه SNMP | Skype | Snort | SolarWinds | Splunk Enterprise | StataCorp Stata | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Ghost Solution Suite | نرم‌افزار بازیابی فاجعه سیستم و داده‌ها | نرم‌افزار مهاجرت سیستم‌ها و برنامه‌ها | نرم‌افزار یکپارچه‌سازی سیستم‌ها | نرم‌افزار TKSoftware RCM | Tableau | Tcpdump | Teradata Database | Transact-SQL | UNIX | UNIX Shell | Ubuntu | VMware | Veritas NetBackup | نرم‌افزار مدیریت شبکه محلی مجازی | نرم‌افزار محاسبات شبکه مجازی VNC | نرم‌افزار شبکه خصوصی مجازی VPN | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Wireshark | Zabbix | jQuery</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -513,22 +513,22 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | خدمات مشتریان و پرسنل | مهندسی و فناوری | مخابرات | ریاضیات | اداری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | مهندسی و فناوری | مخابرات | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مشکل | درک کتبی | سازماندهی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | تشخیص گفتار | بیان کتبی | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | سهولت کار با اعداد | استدلال ریاضی | سرعت ادراکی</t>
+          <t>حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | تشخیص گفتار | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | توانایی عددی | استدلال ریاضی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>داخل ساختمان، محیط کنترل‌شده | ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | فشار زمانی</t>
+          <t>محیط داخلی، دارای کنترل شرایط محیطی | ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | ارتباط با دیگران | صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | تعیین وظایف، اولویت‌ها و اهداف | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | فشار زمانی</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | تست‌کنندگان نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | مدیران وب | توسعه‌دهندگان وب</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | کارشناسان آزمون نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز نصابان خطوط | مدیران وب | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -560,32 +560,32 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>یک زبان برنامه‌نویسی APL | ABC Compiler | ABC: the AspectBench Compiler for AspectJ | AJAX | AWK | Ada | Adobe Acrobat | Adobe ActionScript | Adobe ColdFusion | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe Photoshop | Adobe PostScript | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | زبان الگوریتمی ALGOL | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | موسسه ملی استاندارد آمریکا ANSI C | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | B-Method | Backbone.js | Bash | Basis BBx VisualPRO/5 | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bentley MicroStation | Bigloo Scheme | Bourne Shell | C | C# | C++ | CAST SQL Builder | زبان پردازش تماس CPL | Canu | برگه‌های سبک آبشاری CSS | Chef | نرم‌افزار رایانش ابری Citrix | Clipper | نرم‌افزار تولیدکننده کد | نرم‌افزار اصلاح‌کننده کد | CoffeeCup The HTML Editor | زبان نشانه‌گذاری برنامه مشارکتی CAML | مفسرهای فرمان | سیستم شیء لیسپ مشترک CLOS | زبان مشترک تجاری COBOL | کامپایلرها | سیستم مدیریت داده یکپارچه کامپیوتر Associates CA-IDMS | زبان برنامه‌های آنلاین بلادرنگ کامپیوتر CORAL 66 | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | زبان تعریف داده DDL | زبان دستکاری داده DML | نرم‌افزار اشکال‌زدایی | دکامپایلرها | Delphi Technology | Django | Docker | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان الگوی E++ | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | Embarcadero Delphi | Emerald Software Group Emerald Green Office | Enterprise JavaBeans | Epic Systems | برنامه‌نویسی ماشین‌های حالت رویدادمحور | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | FileMaker Pro | ترجمه فرمول FORTRAN | Forth | Gambit Scheme | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | Greatis Object Inspector | Haskell | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM SPSS Statistics | IBM WebSphere | زبان برنامه‌نویسی ICON | IEA Software Emerald | نرم‌افزار کامپایلر افزایشی | نرم‌افزار توسعه‌دهنده کد درون‌خطی | نرم‌افزار محیط توسعه یکپارچه IDE | زبان تعریف رابط IDL | نرم‌افزار مفسر | اتصال بین ایالتی ICON | J | JUnit | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | زبان کنترل کار JCL | Jupyter Notebook | کامپایلر درجا | KornShell | LAMP Stack | Linux | زبان پردازش لیست LISP | نرم‌افزار طراحی لوگو | نرم‌افزار اشکال‌زدایی سطح پایین | MUMPS M | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft ESP SDK | Microsoft Excel | Microsoft Exchange | زبان نشانه‌گذاری برنامه توسعه‌پذیر مایکروسافت (XAML) | Microsoft FrontPage | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Silverlight | Microsoft Systems Management Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual FoxPro | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | تولیدکننده کد ترکیبی | Modula | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | سیستم‌های پیشگیری از نفوذ به شبکه NIPS | NoSQL | Node.js | Oberon | Objective C | Objective Caml | نرم‌افزار کامپایلر تک‌گذره | OpenAI ChatGPT | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار تولیدکننده کلاس جزئی | Pascal | نرم‌افزار Perforce Helix | Perl | PostgreSQL | PowerSoft PowerBuilder | زبان برنامه‌نویسی یک PL/I | Progress OpenEdge ABL | Progress Sonic ESB | Progress WebSpeed Workshop | Prolog | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | ReCrystallize Crystal Reports | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | مجری توسعه‌یافته بازسازی‌شده REXX | کامپایلر با قابلیت تغییر هدف | نرم‌افزار کنترل نسخه | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | SAP NetWeaver BW | نرم‌افزار SAP | SAS | Salesforce Visualforce | Scala | Scheme | Selenium | شل اسکریپت | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | Smalltalk | Snort | نرم‌افزار ویرایشگر کد منبع | نرم‌افزار مهاجرت کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | زبان نمادین رشته‌محور SNOBOL | گزارش پرس‌وجوی ساختاریافته SQR | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Visual Cafe | نرم‌افزار اشکال‌زدایی نمادین | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | کامپایلر کد نخی | نرم‌افزار تولیدکننده لایه | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Verilog | Veritas NetBackup | Virage VS Archive | نرم‌افزار شبکه خصوصی مجازی VPN | زبان تعریف وب‌سرویس WDSL | Wireshark | نرم‌افزار جریان کار | Xerces2 Java Parser | dBASE Plus | jQuery</t>
+          <t>زبان برنامه‌نویسی APL | ABC Compiler | ABC: the AspectBench Compiler for AspectJ | AJAX | AWK | Ada | Adobe Acrobat | Adobe ActionScript | Adobe ColdFusion | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe Photoshop | Adobe PostScript | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | زبان الگوریتمی ALGOL | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | موسسه ملی استاندارد آمریکا ANSI C | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | B-Method | Backbone.js | Bash | Basis BBx VisualPRO/5 | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bentley MicroStation | Bigloo Scheme | Bourne Shell | C | C# | C++ | CAST SQL Builder | زبان پردازش تماس CPL | Canu | برگه‌های سبک آبشاری CSS | Chef | نرم‌افزار رایانش ابری Citrix | Clipper | نرم‌افزار تولیدکننده کد | نرم‌افزار اصلاح‌کننده کد | CoffeeCup The HTML Editor | زبان نشانه‌گذاری برنامه مشارکتی CAML | مفسرهای فرمان | سیستم شیء لیسپ مشترک CLOS | زبان مشترک تجاری COBOL | کامپایلرها | سیستم مدیریت داده یکپارچه کامپیوتر Associates CA-IDMS | زبان برنامه‌های آنلاین بلادرنگ کامپیوتر CORAL 66 | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | Corel CorelDraw Graphics Suite | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | زبان تعریف داده DDL | زبان دستکاری داده DML | نرم‌افزار عیب‌یابی | دکامپایلرها | Delphi Technology | Django | Docker | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | زبان الگوی E++ | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | Embarcadero Delphi | Emerald Software Group Emerald Green Office | Enterprise JavaBeans | Epic Systems | برنامه‌نویسی ماشین‌های حالت رویدادمحور | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | FileMaker Pro | Formula translation/translator FORTRAN | Forth | Gambit Scheme | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Analytics | Google Angular | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | Greatis Object Inspector | Haskell | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM SPSS Statistics | IBM WebSphere | زبان برنامه‌نویسی ICON | IEA Software Emerald | نرم‌افزار کامپایلر افزایشی | نرم‌افزار توسعه‌دهنده کد درون‌خطی | نرم‌افزار محیط توسعه یکپارچه IDE | زبان تعریف رابط IDL | نرم‌افزار مفسر | اتصال بین ایالتی ICON | J | JUnit | JavaScript | JavaScript Object Notation JSON | زبان کنترل کار JCL | Jupyter Notebook | کامپایلر درجا | KornShell | LAMP Stack | Linux | زبان پردازش لیست LISP | نرم‌افزار طراحی لوگو | نرم‌افزار اشکال‌زدایی سطح پایین | MUMPS M | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft ESP SDK | Microsoft Excel | Microsoft Exchange | زبان نشانه‌گذاری برنامه توسعه‌پذیر مایکروسافت (XAML) | Microsoft FrontPage | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Silverlight | Microsoft Systems Management Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual FoxPro | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | Minitab | تولیدکننده کد ترکیبی | Modula | MongoDB | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | سیستم‌های پیشگیری از نفوذ شبکه NIPS | NoSQL | Node.js | Oberon | Objective C | Objective Caml | نرم‌افزار کامپایلر تک‌گذره | OpenAI ChatGPT | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle E-Business Suite Financials | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار تولیدکننده کلاس جزئی | Pascal | نرم‌افزار Perforce Helix | Perl | PostgreSQL | PowerSoft PowerBuilder | زبان برنامه‌نویسی یک PL/I | Progress OpenEdge ABL | Progress Sonic ESB | Progress WebSpeed Workshop | Prolog | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | ReCrystallize Crystal Reports | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | مجری توسعه‌یافته بازسازی‌شده REXX | کامپایلر با قابلیت تغییر هدف | نرم‌افزار کنترل نسخه | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Objects | SAP BusinessObjects Data Integrator | SAP Crystal Reports | SAP NetWeaver BW | نرم‌افزار SAP | SAS | Salesforce Visualforce | Scala | Scheme | Selenium | Shell script | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | Smalltalk | Snort | نرم‌افزار ویرایشگر کد منبع | نرم‌افزار مهاجرت کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | زبان نمادین رشته‌محور SNOBOL | گزارش پرس‌وجوی ساختاریافته SQR | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Visual Cafe | نرم‌افزار اشکال‌زدایی نمادین | Tableau | نرم‌افزار مالیاتی | Teradata Database | The MathWorks MATLAB | کامپایلر کد نخی | نرم‌افزار تولیدکننده لایه | Transact-SQL | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | VMware | Verilog | Veritas NetBackup | Virage VS Archive | نرم‌افزار شبکه خصوصی مجازی VPN | زبان تعریف وب‌سرویس WDSL | Wireshark | نرم‌افزار جریان کار | Xerces2 Java Parser | dBASE Plus | jQuery</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | خدمات مشتریان و پرسنل | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | بینایی نزدیک | درک شفاهی | حساسیت به مشکل | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | بیان شفاهی | بیان کتبی | تشخیص گفتار | سهولت کار با اعداد | استدلال ریاضی | وضوح گفتار | توجه انتخابی | روان بودن ایده‌ها | اصالت | انعطاف‌پذیری بستار</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | بیان کتبی | تشخیص گفتار | توانایی عددی | استدلال ریاضی | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | اهمیت دقیق بودن یا صحت بالا | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فشار زمانی | سطح رقابت</t>
+          <t>ایمیل | صرف زمان برای نشستن | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | ارتباط با دیگران | فشار زمانی | سطح رقابت</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان ابزارهای کنترل عددی کامپیوتری | اساتید علوم کامپیوتر، تحصیلات تکمیلی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | دانشمندان تحقیقات کامپیوتر و اطلاعات | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان ابزار کنترل عددی کامپیوتری | اساتید علوم رایانه، پس از متوسطه | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | دانشمندان تحقیقات کامپیوتر و اطلاعات | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -617,7 +617,7 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>3M Post-it App | یک زبان برنامه‌نویسی APL | ABC Compiler | ABC: the AspectBench Compiler for AspectJ | ADO.NET | AJAX | AWK | Ada | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | زبان الگوریتمی ALGOL | Allaire ColdFusion | نرم‌افزار Alteryx | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | موسسه ملی استاندارد آمریکا ANSI C | نرم‌افزار Ansible | Apache Airflow | Apache Ant | Apache Avro | Apache Cassandra | Apache Flume | Apache Groovy | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple iOS | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian JIRA | نرم‌افزار نصب خودکار | B-Method | Backbone.js | نرم‌افزار پشتیبان‌گیری و بایگانی | Bash | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bigloo Scheme | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blink | Bootstrap | پروتکل مسیریابی مرزی BGP | C | C# | C++ | زبان پردازش تماس CPL | Canu | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان نشانه‌گذاری برنامه مشارکتی CAML | سیستم شیء لیسپ مشترک CLOS | زبان مشترک تجاری COBOL | نرم‌افزار مدل شیء کامپوننت COM | معماری منطقی مقیاس‌پذیر مبتنی بر کامپوننت CSLA | سیستم مدیریت داده یکپارچه کامپیوتر Associates CA-IDMS | زبان برنامه‌های آنلاین بلادرنگ کامپیوتر CORAL 66 | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار تحلیل داده‌ها | زبان تعریف داده DDL | زبان دستکاری داده DML | DataVision | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار استقرار | سیستم‌عامل دیسک DOS | نرم‌افزار مدل شیء کامپوننت توزیع‌شده DCOM | نرم‌افزار مدیریت پایگاه داده توزیع‌شده | Django | Docker | اسکریپت‌نویسی مدل شیء سند DOM | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Drupal | نرم‌افزار تحلیل پویا | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار مدل‌سازی پویا | زبان الگوی E++ | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eclipse Jersey | Eiffel | Elasticsearch | Embarcadero Delphi | Embarcadero JBuilder | نرم‌افزار توسعه سیستم‌های تعبیه‌شده | Emerald Software Group Emerald Green Office | نرم‌افزار رمزنگاری | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی EAI | برنامه‌نویسی ماشین‌های حالت رویدادمحور | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | FaceTime | نرم‌افزار تست خطا | Figma | نرم‌افزار فایل سرور | FileMaker Pro | نرم‌افزار فایروال | Flipgrid | ترجمه فرمول FORTRAN | Forth | نرم‌افزار تست عملکردی | برنامه دستکاری تصویر گنو GIMP | Gambit Scheme | Git | GitHub | GitLab | Go | Google Analytics | Google Android | Google Angular | نرم‌افزار Google Cloud | Google Docs | Google Drive | Google Gmail | Google Looker Analytics | Google Meet | Google Sheets | Google Sites | Google Slides | Gradle | Grafana Labs Grafana Cloud | GraphQL | نرم‌افزار سازنده رابط کاربری گرافیکی GUI | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | GroupMe | Haskell | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Middleware | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational PurifyPlus | IBM Rational RequisitePro | IBM Rational Rose XDE | IBM SPSS Statistics | IBM Terraform | IBM WebSphere | IBM WebSphere MQ | سیستم‌های عامل IBM z/OS | زبان برنامه‌نویسی ICON | IEA Software Emerald | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تست یکپارچه‌سازی | زبان تعریف رابط IDL | نرم‌افزار تست تعامل‌پذیری | اتصال بین ایالتی ICON | J | JFrog Artifactory | JUnit | JamBoard | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | نرم‌افزار فریم‌ورک جاوااسکریپت | Jenkins CI | زبان کنترل کار JCL | Jupyter Notebook | KornShell | Kotlin | Kubernetes | LAMP Stack | LexisNexis | LibreOffice | LinkedIn | Linux | زبان پردازش لیست LISP | نرم‌افزار تست بارگذاری | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | MUMPS M | Magellan Firmware | سیستم‌های اطلاعات مدیریت MIS | Marketo Marketing Automation | MathWorks Simulink | McAfee | MicroStrategy | معماری میکروسرویس | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft DirectX | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft ESP SDK | Microsoft Excel | Microsoft Exchange | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power Automate | Microsoft Power BI | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | زبان پرس‌وجوی ساختاریافته تراکنشی مایکروسافت T-SQL | نرم‌افزار مهاجرت | نرم‌افزار تست مهاجرت | Minitab | Modula | MongoDB | Moodle | نرم‌افزار MuleSoft | نرم‌افزار تست جهش | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Oberon | واسطه درخواست شیء گروه مدیریت شیء | Objective C | Objective Caml | کتابخانه گرافیکی باز OpenGL | OpenAI ChatGPT | پوسته‌های سیستم‌عامل | Oracle Application Server | Oracle Business Intelligence Discoverer | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Suite | نرم‌افزار Oracle Cloud | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | پلتفرم جاوا ۲ نسخه سازمانی J2EE | سرویس پیام جاوا JMS | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Reports | Oracle SQL Developer | Oracle Solaris | Oracle WebLogic Server | PHP | Pascal | نرم‌افزار مدیریت وصله | نرم‌افزار Perforce Helix | Perl | پلتفرم به عنوان سرویس PaaS | PostgreSQL | زبان برنامه‌نویسی یک PL/I | Prolog | Prometheus | PuTTY | Puppet | PyTorch | Python | QNX | Qlik Tech QlikView | Quest Erwin Data Modeler | R | RESTful API | RabbitMQ | React | React Native | React Redux | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار تست بازیابی | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redis | نرم‌افزار تست رگرسیون | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار مدیریت نیازمندی‌ها | مجری توسعه‌یافته بازسازی‌شده REXX | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Intelligence | SAP Business Objects | SAP Crystal Reports | SAP ERP | SAP NetWeaver | SAP PowerBuilder | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Scheme | Screencastify | نرم‌افزار تست امنیت | Selenium | ServiceNow | شل اسکریپت | رابط برنامه‌نویسی ساده برای XML SAX | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | ورود یکباره SSO | Skype | Slack | Smalltalk | SmugMug Flickr | Snowflake | سایت‌های رسانه‌های اجتماعی | ابزارهای توسعه نرم‌افزار | نرم‌افزار مدیریت توزیع نرم‌افزار | کتابخانه‌های نرم‌افزاری | SonarQube | نرم‌افزار ویرایشگر کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار تحلیل ایستا | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار تست استرس | زبان نمادین رشته‌محور SNOBOL | گزارش پرس‌وجوی ساختاریافته SQR | زبان پرس‌وجوی ساختاریافته SQL | رابط برنامه‌نویسی ماندگاری جاوا سان مایکروسیستمز | Swift | Symantec Visual Cafe | نرم‌افزار تست سیستم | Tableau | Talend Big Data Integration | Talend Data Fabric | TensorFlow | Teradata Database | نرم‌افزار طراحی تست | نرم‌افزار اجرای تست | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | نرم‌افزار تست واحد | نرم‌افزار تست کاربردپذیری | VMware | Verilog | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | Visible Razor | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Vue.js | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار وب سرور | زبان تعریف وب‌سرویس WDSL | Win CE | Wind River VxWorks | Wireshark | WordPress | نرم‌افزار Workday | زبان مسیر XML XPATH | Xcode | YouTube | Zoom | jQuery</t>
+          <t>3M Post-it App | زبان برنامه‌نویسی APL | ABC Compiler | ABC: the AspectBench Compiler for AspectJ | ADO.NET | AJAX | AWK | Ada | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | زبان الگوریتمی ALGOL | Allaire ColdFusion | نرم‌افزار Alteryx | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | موسسه ملی استاندارد آمریکا ANSI C | نرم‌افزار Ansible | Apache Airflow | Apache Ant | Apache Avro | Apache Cassandra | Apache Flume | Apache Groovy | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple iOS | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian JIRA | نرم‌افزار نصب خودکار | B-Method | Backbone.js | نرم‌افزار پشتیبان‌گیری و بایگانی | Bash | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bigloo Scheme | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blink | Bootstrap | پروتکل مسیریابی مرزی BGP | C | C# | C++ | زبان پردازش تماس CPL | Canu | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان نشانه‌گذاری برنامه مشارکتی CAML | سیستم شیء لیسپ مشترک CLOS | زبان مشترک تجاری COBOL | نرم‌افزار مدل شیء کامپوننت COM | معماری منطقی مقیاس‌پذیر مبتنی بر کامپوننت CSLA | سیستم مدیریت داده یکپارچه کامپیوتر Associates CA-IDMS | زبان برنامه‌های آنلاین بلادرنگ کامپیوتر CORAL 66 | سیستم کنترل اطلاعات مشتری CICS | نرم‌افزار تحلیل داده | زبان تعریف داده DDL | زبان دستکاری داده DML | DataVision | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار استقرار | سیستم‌عامل دیسک DOS | نرم‌افزار مدل شیء کامپوننت توزیع‌شده DCOM | نرم‌افزار مدیریت پایگاه داده توزیع‌شده | Django | Docker | اسکریپت‌نویسی مدل شیء سند DOM | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Drupal | نرم‌افزار تحلیل پویا | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار مدل‌سازی پویا | زبان الگوی E++ | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eclipse Jersey | Eiffel | Elasticsearch | Embarcadero Delphi | Embarcadero JBuilder | نرم‌افزار توسعه سیستم‌های تعبیه‌شده | Emerald Software Group Emerald Green Office | نرم‌افزار رمزگذاری | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | برنامه‌نویسی ماشین‌های حالت رویدادمحور | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | FaceTime | نرم‌افزار تست خطا | Figma | نرم‌افزار فایل سرور | FileMaker Pro | نرم‌افزار فایروال | Flipgrid | Formula translation/translator FORTRAN | Forth | نرم‌افزار تست عملکردی | برنامه دستکاری تصویر گنو GIMP | Gambit Scheme | Git | GitHub | GitLab | Go | Google Analytics | Google Android | Google Angular | نرم‌افزار Google Cloud | Google Docs | Google Drive | Google Gmail | Google Looker Analytics | Google Meet | Google Sheets | Google Sites | Google Slides | Gradle | Grafana Labs Grafana Cloud | GraphQL | نرم‌افزار سازنده رابط کاربری گرافیکی GUI | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | GroupMe | Haskell | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Middleware | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational PurifyPlus | IBM Rational RequisitePro | IBM Rational Rose XDE | IBM SPSS Statistics | IBM Terraform | IBM WebSphere | IBM WebSphere MQ | سیستم‌های عامل IBM z/OS | زبان برنامه‌نویسی ICON | IEA Software Emerald | نرم‌افزار Informatica | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تست یکپارچه‌سازی | زبان تعریف رابط IDL | نرم‌افزار تست تعامل‌پذیری | اتصال بین ایالتی ICON | J | JFrog Artifactory | JUnit | JamBoard | JavaScript | JavaScript Object Notation JSON | نرم‌افزار فریم‌ورک جاوااسکریپت | Jenkins CI | زبان کنترل کار JCL | Jupyter Notebook | KornShell | Kotlin | Kubernetes | LAMP Stack | LexisNexis | LibreOffice | LinkedIn | Linux | زبان پردازش لیست LISP | نرم‌افزار تست بارگذاری | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | MUMPS M | Magellan Firmware | سیستم‌های اطلاعات مدیریت MIS | Marketo Marketing Automation | MathWorks Simulink | McAfee | MicroStrategy | معماری میکروسرویس‌ها | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft DirectX | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft ESP SDK | Microsoft Excel | Microsoft Exchange | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Power Automate | Microsoft Power BI | نرم‌افزار Microsoft Power Platform | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | Microsoft Word | زبان پرس‌وجوی ساختاریافته تراکنشی مایکروسافت T-SQL | نرم‌افزار مهاجرت | نرم‌افزار تست مهاجرت | Minitab | Modula | MongoDB | Moodle | نرم‌افزار MuleSoft | نرم‌افزار تست جهش | MySQL | Nagios | National Instruments LabVIEW | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Oberon | واسطه درخواست شیء گروه مدیریت شیء | Objective C | Objective Caml | کتابخانه گرافیکی باز OpenGL | OpenAI ChatGPT | پوسته‌های سیستم‌عامل | Oracle Application Server | Oracle Business Intelligence Discoverer | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Suite | Oracle Cloud software | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | سرویس پیام جاوا JMS | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Reports | Oracle SQL Developer | Oracle Solaris | Oracle WebLogic Server | PHP | Pascal | نرم‌افزار مدیریت وصله | نرم‌افزار Perforce Helix | Perl | پلتفرم به عنوان سرویس PaaS | PostgreSQL | زبان برنامه‌نویسی یک PL/I | Prolog | Prometheus | PuTTY | Puppet | PyTorch | Python | QNX | Qlik Tech QlikView | Quest Erwin Data Modeler | R | RESTful API | RabbitMQ | React | React Native | React Redux | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار تست بازیابی | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redis | نرم‌افزار تست رگرسیون | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار مدیریت الزامات | مجری توسعه‌یافته بازسازی‌شده REXX | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Intelligence | SAP Business Objects | SAP Crystal Reports | SAP ERP | SAP NetWeaver | SAP PowerBuilder | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Scheme | Screencastify | نرم‌افزار تست امنیت | Selenium | ServiceNow | Shell script | رابط برنامه‌نویسی ساده برای XML SAX | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | ورود یکباره SSO | Skype | Slack | Smalltalk | SmugMug Flickr | Snowflake | سایت‌های رسانه‌های اجتماعی | ابزارهای توسعه نرم‌افزار | نرم‌افزار مدیریت توزیع نرم‌افزار | کتابخانه‌های نرم‌افزاری | SonarQube | نرم‌افزار ویرایشگر کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار تحلیل ایستا | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار تست استرس | زبان نمادین رشته‌محور SNOBOL | گزارش پرس‌وجوی ساختاریافته SQR | زبان پرس‌وجوی ساختاریافته SQL | رابط برنامه‌نویسی ماندگاری جاوا سان مایکروسیستمز | Swift | Symantec Visual Cafe | نرم‌افزار تست سیستم | Tableau | Talend Big Data Integration | Talend Data Fabric | TensorFlow | Teradata Database | نرم‌افزار طراحی تست | نرم‌افزار اجرای تست | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | نرم‌افزار تست واحد | نرم‌افزار تست کاربردپذیری | VMware | Verilog | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | Visible Razor | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Vue.js | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار وب سرور | زبان تعریف وب‌سرویس WDSL | Win CE | Wind River VxWorks | Wireshark | WordPress | نرم‌افزار Workday | زبان مسیر XML XPATH | Xcode | YouTube | Zoom | jQuery</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -627,22 +627,22 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ریاضیات | خدمات مشتریان و پرسنل | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مشکل | استدلال قیاسی | بینایی نزدیک | سازماندهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | روان بودن ایده‌ها | توجه انتخابی | اصالت | وضوح گفتار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | اصالت | وضوح گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت نشسته | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
+          <t>صرف زمان برای نشستن | کار با یا مشارکت در یک گروه کاری یا تیم | ایمیل | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | مهندسان الکترونیک، به جز کامپیوتر | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | متخصصان مدیریت پروژه | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران کامپیوتر و سیستم‌های اطلاعاتی | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | مهندسان الکترونیک، به جز کامپیوتر | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | متخصصان مدیریت پروژه | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -674,7 +674,7 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>3M Post-it App | یک زبان برنامه‌نویسی APL | ABC Compiler | ABC: the AspectBench Compiler for AspectJ | ADO.NET | AJAX | AWK | Acresso InstallAnywhere | Ada | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | زبان الگوریتمی ALGOL | Allaire ColdFusion | Amazon Data Pipeline | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | موسسه ملی استاندارد آمریکا ANSI C | نرم‌افزار Ansible | نرم‌افزار ضد جاسوس‌افزار | نرم‌افزار آنتی‌ویروس | Apache Ant | Apache Avro | Apache Cassandra | Apache Flume | Apache Groovy | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache JMeter | Apache Kafka | Apache Maven | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Struts | Apache Subversion SVN | Apache Tomcat | Appium | Apple Cocoa | Apple Safari | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | نرم‌افزار نصب خودکار | B-Method | Backbone.js | نرم‌افزار پشتیبان‌گیری و بایگانی | Bash | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bentley MicroStation | Bigloo Scheme | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blink | Borland SilkTest | Bugzilla | C | C# | C++ | زبان پردازش تماس CPL | Canu | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان نشانه‌گذاری برنامه مشارکتی CAML | سیستم شیء لیسپ مشترک CLOS | زبان مشترک تجاری COBOL | نرم‌افزار مدل شیء کامپوننت COM | معماری منطقی مقیاس‌پذیر مبتنی بر کامپوننت CSLA | سیستم مدیریت داده یکپارچه کامپیوتر Associates CA-IDMS | زبان برنامه‌های آنلاین بلادرنگ کامپیوتر CORAL 66 | CruiseControl | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | نرم‌افزار تحلیل داده‌ها | زبان تعریف داده DDL | زبان دستکاری داده DML | DataVision | Debugview | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار استقرار | سیستم‌عامل دیسک DOS | نرم‌افزار مدل شیء کامپوننت توزیع‌شده DCOM | نرم‌افزار مدیریت پایگاه داده توزیع‌شده | Django | Docker | اسکریپت‌نویسی مدل شیء سند DOM | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Drupal | نرم‌افزار تحلیل پویا | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار مدل‌سازی پویا | زبان الگوی E++ | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | Embarcadero Delphi | Embarcadero JBuilder | نرم‌افزار توسعه سیستم‌های تعبیه‌شده | Emerald Software Group Emerald Green Office | نرم‌افزار رمزنگاری | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی EAI | Epic Systems | برنامه‌نویسی ماشین‌های حالت رویدادمحور | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | FaceTime | نرم‌افزار تست خطا | نرم‌افزار فایل سرور | FileMaker Pro | FileMon | نرم‌افزار فایروال | FitNesse | Flipgrid | ترجمه فرمول FORTRAN | Forth | نرم‌افزار تست عملکردی | برنامه دستکاری تصویر گنو GIMP | Gambit Scheme | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | GitLab | Go | Google Analytics | Google Android | Google Angular | Google Docs | Google Drive | Google Gmail | Google Meet | Google Sheets | Google Sites | Google Slides | نرم‌افزار سازنده رابط کاربری گرافیکی GUI | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | GroupMe | Haskell | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hewlett-Packard HP QuickTest Professional | Hewlett-Packard HP TestDirector for Quality Center | Hewlett-Packard HP WinRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Middleware | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational PurifyPlus | IBM Rational RequisitePro | IBM Rational Robot | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | سیستم‌های عامل IBM z/OS | زبان برنامه‌نویسی ICON | IEA Software Emerald | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تست یکپارچه‌سازی | زبان تعریف رابط IDL | نرم‌افزار تست تعامل‌پذیری | اتصال بین ایالتی ICON | J | JUnit | JamBoard | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | Jenkins CI | JetBrains IntelliJ IDEA | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | LexisNexis | LibreOffice | LinkedIn | Linux | زبان پردازش لیست LISP | نرم‌افزار تست بارگذاری | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | MUMPS M | Magellan Firmware | MathWorks Simulink | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft DirectX | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft ESP SDK | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Playwright | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual SourceSafe | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows SDK | Microsoft Windows Server | Microsoft Word | زبان پرس‌وجوی ساختاریافته تراکنشی مایکروسافت T-SQL | نرم‌افزار مهاجرت | نرم‌افزار تست مهاجرت | Minitab | Modula | MongoDB | Moodle | Mozilla Firefox | نرم‌افزار تست جهش | MySQL | NUnit | Nagios | National Instruments LabVIEW | NetSuite ERP | نرم‌افزار تشخیص نفوذ به شبکه | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Oberon | واسطه درخواست شیء گروه مدیریت شیء | Objective C | Objective Caml | کتابخانه گرافیکی باز OpenGL | پوسته‌های سیستم‌عامل | Oracle Application Server | Oracle Business Intelligence Discoverer | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Suite | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | پلتفرم جاوا ۲ نسخه سازمانی J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Reports | Oracle Solaris | Oracle WebLogic Server | PHP | Pascal | نرم‌افزار مدیریت وصله | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Postman | زبان برنامه‌نویسی یک PL/I | Prolog | PuTTY | Puppet | Python | QNX | Qlik Tech QlikView | Quest Erwin Data Modeler | R | REST Assured | RESTful API | React | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار تست بازیابی | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | RegMon | نرم‌افزار تست رگرسیون | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار مدیریت نیازمندی‌ها | مجری توسعه‌یافته بازسازی‌شده REXX | نرم‌افزار کنترل نسخه | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Intelligence | SAP Business Objects | SAP Crystal Reports | SAP NetWeaver | SAP PowerBuilder | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Scheme | Screencastify | نرم‌افزار تست امنیت | Selenium | شل اسکریپت | رابط برنامه‌نویسی ساده برای XML SAX | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | Skype | Slack | Smalltalk | SmartBear Software AutomatedQA TestComplete | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | نرم‌افزار مدیریت توزیع نرم‌افزار | نرم‌افزار ویرایشگر کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار تحلیل ایستا | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار تست استرس | زبان نمادین رشته‌محور SNOBOL | گزارش پرس‌وجوی ساختاریافته SQR | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Visual Cafe | نرم‌افزار تست سیستم | Tableau | Talend Big Data Integration | Talend Data Fabric | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار طراحی تست | نرم‌افزار اجرای تست | TestNG | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | Twiki | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | نرم‌افزار تست واحد | نرم‌افزار تست کاربردپذیری | VMWare ESX Server | VMWare Workstation | VMware | Verilog | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | Visible Razor | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Watir | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار مرورگر وب | نرم‌افزار وب سرور | زبان تعریف وب‌سرویس WDSL | Win CE | Wind River Systems VxWorks | Wind River VxWorks | Wireshark | نرم‌افزار جریان کار | زبان مسیر XML XPATH | Xcode | YouTube | YourKit Java Profiler | Zoom | ej-technologies JProfiler | jQuery</t>
+          <t>3M Post-it App | زبان برنامه‌نویسی APL | ABC Compiler | ABC: the AspectBench Compiler for AspectJ | ADO.NET | AJAX | AWK | Acresso InstallAnywhere | Ada | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | زبان الگوریتمی ALGOL | Allaire ColdFusion | Amazon Data Pipeline | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | موسسه ملی استاندارد آمریکا ANSI C | نرم‌افزار Ansible | نرم‌افزار ضد جاسوس‌افزار | نرم‌افزار آنتی‌ویروس | Apache Ant | Apache Avro | Apache Cassandra | Apache Flume | Apache Groovy | Apache HBase | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache JMeter | Apache Kafka | Apache Maven | Apache Oozie | Apache Pig | Apache Solr | Apache Spark | Apache Sqoop | Apache Struts | Apache Subversion SVN | Apache Tomcat | Appium | Apple Cocoa | Apple Safari | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian JIRA | Autodesk AutoCAD | نرم‌افزار نصب خودکار | B-Method | Backbone.js | نرم‌افزار پشتیبان‌گیری و بایگانی | Bash | دستورالعمل نمادین همه‌منظوره مبتدیان BASIC | Bentley MicroStation | Bigloo Scheme | Blackbaud The Raiser's Edge | نرم‌افزار Blackboard | Blink | Borland SilkTest | Bugzilla | C | C# | C++ | زبان پردازش تماس CPL | Canu | برگه‌های سبک آبشاری CSS | Chef | Cisco IOS | Cisco Webex | نرم‌افزار رایانش ابری Citrix | زبان نشانه‌گذاری برنامه مشارکتی CAML | سیستم شیء لیسپ مشترک CLOS | زبان مشترک تجاری COBOL | نرم‌افزار مدل شیء کامپوننت COM | معماری منطقی مقیاس‌پذیر مبتنی بر کامپوننت CSLA | سیستم مدیریت داده یکپارچه کامپیوتر Associates CA-IDMS | زبان برنامه‌های آنلاین بلادرنگ کامپیوتر CORAL 66 | CruiseControl | سیستم کنترل اطلاعات مشتری CICS | Dassault Systemes CATIA | نرم‌افزار تحلیل داده | زبان تعریف داده DDL | زبان دستکاری داده DML | DataVision | Debugview | نرم‌افزار ردیابی نقص | Delphi Technology | نرم‌افزار استقرار | سیستم‌عامل دیسک DOS | نرم‌افزار مدل شیء کامپوننت توزیع‌شده DCOM | نرم‌افزار مدیریت پایگاه داده توزیع‌شده | Django | Docker | اسکریپت‌نویسی مدل شیء سند DOM | نرم‌افزار سیستم مدیریت اسناد | Dropbox | Drupal | نرم‌افزار تحلیل پویا | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار مدل‌سازی پویا | زبان الگوی E++ | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Eiffel | Elasticsearch | Embarcadero Delphi | Embarcadero JBuilder | نرم‌افزار توسعه سیستم‌های تعبیه‌شده | Emerald Software Group Emerald Green Office | نرم‌افزار رمزگذاری | Enterprise JavaBeans | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Epic Systems | برنامه‌نویسی ماشین‌های حالت رویدادمحور | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | FaceTime | نرم‌افزار تست خطا | نرم‌افزار فایل سرور | FileMaker Pro | FileMon | نرم‌افزار فایروال | FitNesse | Flipgrid | Formula translation/translator FORTRAN | Forth | نرم‌افزار تست عملکردی | برنامه دستکاری تصویر گنو GIMP | Gambit Scheme | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | GitLab | Go | Google Analytics | Google Android | Google Angular | Google Docs | Google Drive | Google Gmail | Google Meet | Google Sheets | Google Sites | Google Slides | نرم‌افزار سازنده رابط کاربری گرافیکی GUI | نرم‌افزار طراحی رابط کاربری گرافیکی GUI | GroupMe | Haskell | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hewlett-Packard HP QuickTest Professional | Hewlett-Packard HP TestDirector for Quality Center | Hewlett-Packard HP WinRunner | Hibernate ORM | نرم‌افزار مدیریت منابع انسانی HRMS | زبان نشانه‌گذاری ابرمتن HTML | IBM AIX | IBM Cognos Impromptu | IBM DB2 | IBM Domino | IBM InfoSphere DataStage | IBM Middleware | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational ClearCase | IBM Rational ClearQuest | IBM Rational PurifyPlus | IBM Rational RequisitePro | IBM Rational Robot | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | سیستم‌های عامل IBM z/OS | زبان برنامه‌نویسی ICON | IEA Software Emerald | نرم‌افزار محیط توسعه یکپارچه IDE | نرم‌افزار تست یکپارچه‌سازی | زبان تعریف رابط IDL | نرم‌افزار تست تعامل‌پذیری | اتصال بین ایالتی ICON | J | JUnit | JamBoard | JavaScript | JavaScript Object Notation JSON | Jenkins CI | JetBrains IntelliJ IDEA | زبان کنترل کار JCL | Jupyter Notebook | KornShell | LAMP Stack | LexisNexis | LibreOffice | LinkedIn | Linux | زبان پردازش لیست LISP | نرم‌افزار تست بارگذاری | LogMeIn GoToMeeting | LogMeIn GoToWebinar | Loom | MUMPS M | Magellan Firmware | MathWorks Simulink | McAfee | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft DirectX | Microsoft Dynamics | Microsoft Dynamics GP | Microsoft ESP SDK | Microsoft Excel | Microsoft Exchange | Microsoft Internet Explorer | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft Playwright | Microsoft PowerPoint | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Team Foundation Server | Microsoft Teams | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual SourceSafe | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows SDK | Microsoft Windows Server | Microsoft Word | زبان پرس‌وجوی ساختاریافته تراکنشی مایکروسافت T-SQL | نرم‌افزار مهاجرت | نرم‌افزار تست مهاجرت | Minitab | Modula | MongoDB | Moodle | Mozilla Firefox | نرم‌افزار تست جهش | MySQL | NUnit | Nagios | National Instruments LabVIEW | NetSuite ERP | نرم‌افزار تشخیص نفوذ شبکه | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Oberon | واسطه درخواست شیء گروه مدیریت شیء | Objective C | Objective Caml | کتابخانه گرافیکی باز OpenGL | پوسته‌های سیستم‌عامل | Oracle Application Server | Oracle Business Intelligence Discoverer | Oracle Business Intelligence Enterprise Edition | Oracle Business Intelligence Suite | Oracle Database | Oracle E-Business Suite Financials | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle PeopleSoft Financials | Oracle Primavera Enterprise Project Portfolio Management | Oracle Reports | Oracle Solaris | Oracle WebLogic Server | PHP | Pascal | نرم‌افزار مدیریت وصله | نرم‌افزار Perforce Helix | Perl | PostgreSQL | Postman | زبان برنامه‌نویسی یک PL/I | Prolog | PuTTY | Puppet | Python | QNX | Qlik Tech QlikView | Quest Erwin Data Modeler | R | REST Assured | RESTful API | React | نرم‌افزار سیستم‌عامل بلادرنگ RTOS | نرم‌افزار تست بازیابی | Red Hat Ansible Engine | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | RegMon | نرم‌افزار تست رگرسیون | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار مدیریت الزامات | مجری توسعه‌یافته بازسازی‌شده REXX | نرم‌افزار کنترل نسخه | Ruby | Ruby on Rails | SAP Adaptive Server Enterprise | SAP Business Intelligence | SAP Business Objects | SAP Crystal Reports | SAP NetWeaver | SAP PowerBuilder | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Scheme | Screencastify | نرم‌افزار تست امنیت | Selenium | Shell script | رابط برنامه‌نویسی ساده برای XML SAX | برنامه شبیه‌سازی با تاکید بر مدارهای مجتمع SPICE | Skype | Slack | Smalltalk | SmartBear Software AutomatedQA TestComplete | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | نرم‌افزار مدیریت توزیع نرم‌افزار | نرم‌افزار ویرایشگر کد منبع | Splunk Enterprise | Spring Boot | Spring Framework | StataCorp Stata | نرم‌افزار تحلیل ایستا | نرم‌افزار شبکه ذخیره‌سازی SAN | نرم‌افزار تست استرس | زبان نمادین رشته‌محور SNOBOL | گزارش پرس‌وجوی ساختاریافته SQR | زبان پرس‌وجوی ساختاریافته SQL | نرم‌افزار کنترل نظارتی و گردآوری داده SCADA | Swift | Symantec Visual Cafe | نرم‌افزار تست سیستم | Tableau | Talend Big Data Integration | Talend Data Fabric | نرم‌افزار مالیاتی | Teradata Database | نرم‌افزار طراحی تست | نرم‌افزار اجرای تست | TestNG | The MathWorks MATLAB | Transact-SQL | Trimble SketchUp Pro | Twiki | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | نرم‌افزار تست واحد | نرم‌افزار تست کاربردپذیری | VMWare ESX Server | VMWare Workstation | VMware | Verilog | Veritas NetBackup | نرم‌افزار کنترل نسخه | نرم‌افزار شبکه خصوصی مجازی VPN | Visible Razor | نرم‌افزار سیستم انتقال صدا روی پروتکل اینترنت VoIP | Watir | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار مرورگر وب | نرم‌افزار وب سرور | زبان تعریف وب‌سرویس WDSL | Win CE | Wind River Systems VxWorks | Wind River VxWorks | Wireshark | نرم‌افزار جریان کار | زبان مسیر XML XPATH | Xcode | YouTube | YourKit Java Profiler | Zoom | ej-technologies JProfiler | jQuery</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -684,22 +684,22 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | طراحی</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مشکل | استدلال قیاسی | استدلال استقرایی | بیان کتبی | سازماندهی اطلاعات | بینایی نزدیک | تشخیص گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روان بودن ایده‌ها | وضوح گفتار | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | وضوح گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان به صورت نشسته | اهمیت دقیق بودن یا صحت بالا | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار کارهای مشابه | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت</t>
+          <t>ایمیل | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | مکالمات تلفنی | ارتباط با دیگران | تعیین وظایف، اولویت‌ها و اهداف | فشار زمانی | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت | سطح رقابت</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | متخصصان و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | تست‌کنندگان نفوذ | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی | طراحان رابط دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | تکنولوژیست‌ها و تکنسین‌های کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به جز کامپیوتر | مهندسان صنایع | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان آزمون نفوذ | تحلیل‌گران کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -731,7 +731,7 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>3M Post-it App | AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Cocoa | Apple Final Cut Pro | Apple Keynote | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian HipChat | Atlassian JIRA | Backbone.js | Bash | نرم‌افزار Blackboard | Blink | Bootstrap | C | C# | C++ | برگه‌های سبک آبشاری CSS | Chef | Cisco Webex | زبان مشترک تجاری COBOL | رابط دروازه مشترک CGI | سیستم کنترل اطلاعات مشتری CICS | Delphi Technology | Django | Docker | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | Enterprise JavaBeans | Epic Systems | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | Facebook | Figma | FileMaker Pro | FlexBox | Flipgrid | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Ads | Google Analytics | Google Android | Google Angular | نرم‌افزار Google Cloud | Google Docs | Google Drive | Google Meet | Google Sites | Google Slides | GraphQL | HashiCorp Vagrant | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Informix | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | نرم‌افزار InVision | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JamBoard | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | نرم‌افزار فریم‌ورک جاوااسکریپت | Jekyll | Jenkins CI | Jest | JetBrains PhpStorm | زبان کنترل کار JCL | Jupyter Notebook | Kapwing | KornShell | Kubernetes | LAMP Stack | LinkedIn | Linux | MarkLogic | Marketo Marketing Automation | MeteorJS | MicroStrategy | معماری میکروسرویس | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Commerce Server | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual InterDev | Microsoft Visual SourceSafe | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | MongoDB | Moodle | MySQL | Nagios | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Nunjucks | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | پلتفرم جاوا ۲ نسخه سازمانی J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار Perforce Helix | Perl | PhantomJS | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | RESTful API | React | React Redux | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redis | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | RequireJS | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Screencast-O-Matic | Screencastify | Selenium | شل اسکریپت | Sitecore CMS | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Splunk Enterprise | Spring Boot | Spring Framework | زبان پرس‌وجوی ساختاریافته SQL | Swift | برگه‌های سبک بسیار جذاب از نظر ساختاری SASS | Tableau | Teradata Database | The MathWorks MATLAB | Transact-SQL | Travis | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | Vue.js | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار سیستم مدیریت محتوای وب CMS | Wireshark | WordPress | YouTube | Zend Framework | jQuery | webpack</t>
+          <t>3M Post-it App | AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Cocoa | Apple Final Cut Pro | Apple Keynote | Apple macOS | Atlassian Bamboo | Atlassian Bitbucket | Atlassian Confluence | Atlassian HipChat | Atlassian JIRA | Backbone.js | Bash | نرم‌افزار Blackboard | Blink | Bootstrap | C | C# | C++ | برگه‌های سبک آبشاری CSS | Chef | Cisco Webex | زبان مشترک تجاری COBOL | رابط دروازه مشترک CGI | سیستم کنترل اطلاعات مشتری CICS | Delphi Technology | Django | Docker | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ESRI ArcGIS | Eclipse IDE | Elasticsearch | Enterprise JavaBeans | Epic Systems | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | Facebook | Figma | FileMaker Pro | FlexBox | Flipgrid | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | Git | GitHub | Go | Google Ads | Google Analytics | Google Android | Google Angular | نرم‌افزار Google Cloud | Google Docs | Google Drive | Google Meet | Google Sites | Google Slides | GraphQL | HashiCorp Vagrant | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Informix | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | نرم‌افزار InVision | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JamBoard | JavaScript | JavaScript Object Notation JSON | نرم‌افزار فریم‌ورک جاوااسکریپت | Jekyll | Jenkins CI | Jest | JetBrains PhpStorm | زبان کنترل کار JCL | Jupyter Notebook | Kapwing | KornShell | Kubernetes | LAMP Stack | LinkedIn | Linux | MarkLogic | Marketo Marketing Automation | MeteorJS | MicroStrategy | معماری میکروسرویس‌ها | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Commerce Server | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual InterDev | Microsoft Visual SourceSafe | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | MongoDB | Moodle | MySQL | Nagios | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Nunjucks | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار Perforce Helix | Perl | PhantomJS | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | RESTful API | React | React Redux | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | Redis | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | نرم‌افزار سیستم مدیریت پایگاه داده رابطه‌ای | RequireJS | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Screencast-O-Matic | Screencastify | Selenium | Shell script | Sitecore CMS | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Splunk Enterprise | Spring Boot | Spring Framework | زبان پرس‌وجوی ساختاریافته SQL | Swift | برگه‌های سبک بسیار جذاب از نظر ساختاری SASS | Tableau | Teradata Database | The MathWorks MATLAB | Transact-SQL | Travis | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | Vue.js | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار سیستم مدیریت محتوای وب CMS | Wireshark | WordPress | YouTube | Zend Framework | jQuery | webpack</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -741,22 +741,22 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | ارتباطات و رسانه</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | ارتباطات و رسانه</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بینایی نزدیک | حساسیت به مشکل | استدلال استقرایی | سازماندهی اطلاعات | وضوح گفتار | تشخیص گفتار | بیان شفاهی | روان بودن ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت | بیان کتبی | سرعت ادراکی</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بیان شفاهی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت | بیان کتبی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>صرف زمان به صورت نشسته | ایمیل | آزادی در تصمیم‌گیری | داخل ساختمان، محیط کنترل‌شده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق بودن یا صحت بالا | اهمیت تکرار کارهای مشابه | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | سطح رقابت | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>صرف زمان برای نشستن | ایمیل | آزادی در تصمیم‌گیری | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | اهمیت دقیق یا درست بودن | اهمیت تکرار وظایف یکسان | مکالمات تلفنی | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | کار با یا مشارکت در یک گروه کاری یا تیم | فشار زمانی | ارتباط با دیگران | سطح رقابت | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | ناشران رومیزی | متخصصان مدیریت اسناد | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | استراتژیست‌های بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | طراحان رابط دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | ناشران رومیزی | متخصصان مدیریت اسناد | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | استراتژیست‌های بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | مدیران وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -788,32 +788,32 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>3M Post-it App | AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe XD | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Cocoa | Apple Keynote | Apple iOS | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Axure RP | Backbone.js | Bash | نرم‌افزار Blackboard | Blink | Bootstrap | C | C# | C++ | برگه‌های سبک آبشاری CSS | نرم‌افزار چت‌بات | Chef | Cisco Webex | زبان مشترک تجاری COBOL | رابط دروازه مشترک CGI | سیستم کنترل اطلاعات مشتری CICS | Delphi Technology | Django | Docker | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Eclipse IDE | Elasticsearch | Enterprise JavaBeans | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | Figma | FileMaker Pro | FlexBox | Flipgrid | Git | GitHub | Go | Google Ads | Google Analytics | Google Android | Google Angular | Google Docs | Google Drive | Google Meet | Google Sites | Google Slides | HashiCorp Vagrant | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Informix | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | نرم‌افزار InVision | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JamBoard | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | Jekyll | JetBrains PhpStorm | زبان کنترل کار JCL | Jupyter Notebook | Kapwing | KornShell | LAMP Stack | Linux | MarkLogic | MeteorJS | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Commerce Server | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual InterDev | Microsoft Visual SourceSafe | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | MongoDB | Moodle | MySQL | Nagios | Nearpod | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Nunjucks | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | پلتفرم جاوا ۲ نسخه سازمانی J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار Perforce Helix | Perl | PhantomJS | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | RequireJS | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Screencast-O-Matic | Screencastify | Selenium | شل اسکریپت | Sitecore CMS | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Splunk Enterprise | Spring Boot | Spring Framework | زبان پرس‌وجوی ساختاریافته SQL | Swift | Tableau | Teradata Database | The MathWorks MATLAB | Transact-SQL | Travis | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | UserZoom | Vue.js | WeVideo | Wireshark | YouTube | Zend Framework | jQuery</t>
+          <t>3M Post-it App | AJAX | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Flex | Adobe Illustrator | Adobe InDesign | Adobe Photoshop | Adobe XD | برنامه‌نویسی پیشرفته برنامه‌های تجاری ABAP | Airtable | Amazon DynamoDB | Amazon Elastic Compute Cloud EC2 | Amazon Kinesis | Amazon Redshift | Amazon Simple Storage Service S3 | Amazon Web Services AWS CloudFormation | نرم‌افزار Amazon Web Services AWS | نرم‌افزار Ansible | Apache Ant | Apache Cassandra | Apache Groovy | Apache HTTP Server | Apache Hadoop | Apache Hive | Apache Kafka | Apache Maven | Apache Pig | Apache Solr | Apache Spark | Apache Struts | Apache Subversion SVN | Apache Tomcat | Apple Cocoa | Apple Keynote | Apple iOS | Apple macOS | Atlassian Bamboo | Atlassian Confluence | Atlassian JIRA | Axure RP | Backbone.js | Bash | نرم‌افزار Blackboard | Blink | Bootstrap | C | C# | C++ | برگه‌های سبک آبشاری CSS | نرم‌افزار چت‌بات | Chef | Cisco Webex | زبان مشترک تجاری COBOL | رابط دروازه مشترک CGI | سیستم کنترل اطلاعات مشتری CICS | Delphi Technology | Django | Docker | Dropbox | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | Eclipse IDE | Elasticsearch | Enterprise JavaBeans | Evernote | Ext JS | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | تبدیلات زبان شیوه‌نامه توسعه‌پذیر XSLT | Figma | FileMaker Pro | FlexBox | Flipgrid | Git | GitHub | Go | Google Ads | Google Analytics | Google Android | Google Angular | Google Docs | Google Drive | Google Meet | Google Sites | Google Slides | HashiCorp Vagrant | Hewlett Packard HP-UX | Hewlett Packard LoadRunner | Hibernate ORM | نرم‌افزار HubSpot | زبان نشانه‌گذاری ابرمتن HTML | IBM Cognos Impromptu | IBM Domino | IBM InfoSphere DataStage | IBM Informix | IBM Notes | نرم‌افزار IBM Power Systems | IBM Rational Rose XDE | IBM SPSS Statistics | IBM WebSphere | نرم‌افزار InVision | نرم‌افزار محیط توسعه یکپارچه IDE | JUnit | JamBoard | JavaScript | JavaScript Object Notation JSON | Jekyll | JetBrains PhpStorm | زبان کنترل کار JCL | Jupyter Notebook | Kapwing | KornShell | LAMP Stack | Linux | MarkLogic | MeteorJS | MicroStrategy | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft ASP.NET Core MVC | Microsoft Access | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft Commerce Server | Microsoft Dynamics | Microsoft Excel | Microsoft Internet Information Services (IIS) | نرم‌افزار Microsoft Office | Microsoft PowerShell | Microsoft Project | Microsoft Publisher | Microsoft SQL Server | Microsoft SQL Server Integration Services SSIS | Microsoft SQL Server Reporting Services SSRS | Microsoft SharePoint | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Basic.NET | Microsoft Visual C# .NET | Microsoft Visual InterDev | Microsoft Visual SourceSafe | Microsoft Visual Studio | Microsoft Windows | Microsoft Windows Server | MongoDB | Moodle | MySQL | Nagios | Nearpod | NetSuite ERP | NoSQL | Node.js | نرم‌افزار امنیت سایبری NortonLifeLock | Nunjucks | Objective C | Oracle Business Intelligence Enterprise Edition | Oracle Database | Oracle Eloqua | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle Hyperion | Oracle JD Edwards EnterpriseOne | Oracle JDBC | Oracle Java | Oracle Java 2 Platform Enterprise Edition J2EE | Oracle JavaServer Pages JSP | Oracle PL/SQL | Oracle PeopleSoft | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle WebLogic Server | PHP | نرم‌افزار Perforce Helix | Perl | PhantomJS | PostgreSQL | Puppet | Python | Qlik Tech QlikView | Quest Erwin Data Modeler | R | React | Red Hat Enterprise Linux | Red Hat OpenShift | Red Hat WildFly | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | RequireJS | Ruby | Ruby on Rails | SAP Business Objects | SAP Crystal Reports | نرم‌افزار SAP | SAS | Salesforce Visualforce | نرم‌افزار Salesforce | Scala | Screencast-O-Matic | Screencastify | Selenium | Shell script | Sitecore CMS | Skype | Slack | SmugMug Flickr | سایت‌های رسانه‌های اجتماعی | Splunk Enterprise | Spring Boot | Spring Framework | زبان پرس‌وجوی ساختاریافته SQL | Swift | Tableau | Teradata Database | The MathWorks MATLAB | Transact-SQL | Travis | Trimble SketchUp Pro | TypeScript | UNIX | UNIX Shell | Ubuntu | زبان مدل‌سازی یکپارچه UML | UserZoom | Vue.js | WeVideo | Wireshark | YouTube | Zend Framework | jQuery</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | طراحی | زبان انگلیسی | ارتباطات و رسانه | خدمات مشتریان و پرسنل | ریاضیات | هنرهای زیبا | فروش و بازاریابی | مهندسی و فناوری</t>
+          <t>رایانه و الکترونیک | طراحی | زبان انگلیسی | ارتباطات و رسانه | خدمات مشتری و شخصی | ریاضیات | هنرهای زیبا | فروش و بازاریابی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مشکل | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | سهولت کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار | تشخیص رنگ بصری</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار کارهای مشابه | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | سطح رقابت | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | ناشران رومیزی | متخصصان مدیریت اسناد | طراحان گرافیک | مدیران شبکه و سیستم‌های کامپیوتری | استراتژیست‌های بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | طراحان بازی‌های ویدئویی | مدیران وب | توسعه‌دهندگان وب</t>
+          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | ناشران رومیزی | متخصصان مدیریت اسناد | طراحان گرافیک | مدیران شبکه و سیستم‌های کامپیوتری | استراتژیست‌های بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | طراحان بازی‌های ویدئویی | مدیران وب | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -855,22 +855,22 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>طراحی | کامپیوتر و الکترونیک | ارتباطات و رسانه | روان‌شناسی | ریاضیات | زبان انگلیسی</t>
+          <t>طراحی | رایانه و الکترونیک | ارتباطات و رسانه | روان‌شناسی | ریاضیات | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>روان بودن ایده‌ها | درک کتبی | اصالت | بینایی نزدیک | سازماندهی اطلاعات | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مشکل | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | تجسم | تشخیص گفتار | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
+          <t>روانی ایده‌ها | درک کتبی | اصالت | بینایی نزدیک | ترتیب‌دهی اطلاعات | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | تجسم | تشخیص گفتار | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | داخل ساختمان، محیط کنترل‌شده | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | فشار زمانی | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | کار با یا مشارکت در یک گروه کاری یا تیم | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | سطح رقابت | فشار زمانی | صرف زمان برای انجام حرکات تکراری | تعیین وظایف، اولویت‌ها و اهداف | ارتباط با دیگران | آزادی در تصمیم‌گیری | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران هنری | تکنسین‌های صدا و تصویر | طراحان تجاری و صنعتی | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | مهندسان/معماران سیستم‌های کامپیوتری | دانشمندان تحقیقات کامپیوتر و اطلاعات | ناشران رومیزی | تدوین‌گران فیلم و ویدئو | هنرمندان هنرهای زیبا، از جمله نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | تهیه‌کنندگان و کارگردانان | استراتژیست‌های بازاریابی موتورهای جستجو | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
+          <t>مدیران هنری | تکنسین‌های صوتی و تصویری | طراحان تجاری و صنعتی | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | مهندسان و معماران سامانه‌های رایانه‌ای | دانشمندان تحقیقات کامپیوتر و اطلاعات | ناشران رومیزی | تدوینگران فیلم و ویدئو | هنرمندان تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | تهیه‌کنندگان و کارگردانان | استراتژیست‌های بازاریابی جستجو | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران وب | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,27 +907,27 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | مخابرات | مدیریت و امور اداری | خدمات مشتریان و پرسنل | آموزش و پرورش | طراحی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | مخابرات | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | طراحی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | حساسیت به مشکل | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | اصالت | توجه انتخابی | اشتراک زمانی | تجسم | حفظ کردن | استدلال ریاضی | سهولت کار با اعداد | سرعت ادراکی | انعطاف‌پذیری بستار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق بودن یا صحت بالا | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تاثیر تصمیمات بر همکاران یا نتایج شرکت | سروکار داشتن با مشتریان خارجی یا عموم مردم به طور کلی | اهمیت تکرار کارهای مشابه | میزان اتوماسیون | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | ارتباط با دیگران | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | تعیین وظایف، اولویت‌ها و اهداف | اهمیت دقیق یا درست بودن | فشار زمانی | نامه‌ها و یادداشت‌های کتبی | فراوانی تصمیم‌گیری | تأثیر تصمیمات بر همکاران یا نتایج شرکت | تعامل با مشتریان خارجی یا عموم مردم | اهمیت تکرار وظایف یکسان | میزان خودکارسازی | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران وب | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | متخصصان مدیریت اسناد | تست‌کنندگان نفوذ | مهندسان امنیت اطلاعات | تحلیل‌گران جرم‌شناسی دیجیتال | مهندسان بلاکچین | مهندسان/معماران سیستم‌های کامپیوتری | مدیران پروژه فناوری اطلاعات | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران امنیت اطلاعات | معماران شبکه کامپیوتری | مدیران شبکه و سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | توسعه‌دهندگان نرم‌افزار | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان وب | متخصصان پشتیبانی شبکه کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری</t>
+          <t>مدیران وب | متخصصان و تکنسین‌های سیستم‌های اطلاعات جغرافیایی | متخصصان مدیریت اسناد | کارشناسان آزمون نفوذ | مهندسان امنیت اطلاعات | تحلیل‌گران جرم‌شناسی دیجیتال | مهندسان بلاک‌چین | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران پروژه فناوری اطلاعات | تحلیلگران سیستم‌های کامپیوتری | تحلیل‌گران امنیت اطلاعات | معماران شبکه کامپیوتری | مدیران شبکه و سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | توسعه‌دهندگان نرم‌افزار | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان وب | متخصصان پشتیبانی شبکه کامپیوتری | مدیران کامپیوتر و سیستم‌های اطلاعاتی</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -959,32 +959,32 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>AJAX | Adobe Acrobat | Adobe ActionScript | Adobe ColdFusion | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Dreamweaver | Adobe Experience Manager (AEM) | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Macromedia HomeSite | Adobe PageMaker | Adobe Photoshop | نرم‌افزار Amazon Web Services AWS | Apache Ant | Apache HTTP Server | Apache Struts | Apache Tomcat | Apple Safari | Berkeley Internet Domain Name BIND | CA SiteMinder | برگه‌های سبک آبشاری CSS | نرم‌افزار رایانش ابری Citrix | رابط دروازه مشترک CGI | سیستم‌های مدیریت محتوا CMS | Corel CorelDraw Graphics Suite | سیستم کنترل اطلاعات مشتری CICS | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ایمیل | Embarcadero Delphi | Enterprise JavaBeans | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | نرم‌افزار فایروال | Google Ads | Google Analytics | Hewlett Packard HP-UX | زبان نشانه‌گذاری ابرمتن HTML | IBM Middleware | IBM WebSphere | IBM WebSphere MQ | JavaScript | Joomla | Juniper Networks NetScreen-Security Manager | KornShell | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft DNS Server | Microsoft Excel | Microsoft Exchange | Microsoft FrontPage | Microsoft Internet Explorer | Microsoft Internet Information Services (IIS) | Microsoft Internet Information Services (IIS) Manager | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Virtual Server | Microsoft Visio | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Mozilla Firefox | MySQL | OpenText Livelink ECM | Oracle Application Server | Oracle Business Intelligence Enterprise Edition | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle WebLogic Server | PHP | Perl | PostgreSQL | Python | RESTful API | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار روتر | SAS | Salesforce Marketing Cloud | شل اسکریپت | ابزارهای توسعه نرم‌افزار | Sony Sound Forge | Sorenson Media Sorenson Squeeze | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java Servlet API | نرم‌افزار سوئیچ | زبان فرمان ابزار Tcl | UNIX | VMWare ESX Server | Vignette Content Management | Vignette Portal | نرم‌افزار فریم‌ورک برنامه‌های کاربردی وب | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار سیستم مدیریت محتوای وب CMS | نرم‌افزار وب سرور | WebTrends Analytics | WordPress | jQuery</t>
+          <t>AJAX | Adobe Acrobat | Adobe ActionScript | Adobe ColdFusion | نرم‌افزار Adobe Creative Cloud | Adobe Director | Adobe Dreamweaver | Adobe Experience Manager (AEM) | Adobe FreeHand MX | Adobe Illustrator | Adobe InDesign | Adobe Macromedia HomeSite | Adobe PageMaker | Adobe Photoshop | نرم‌افزار Amazon Web Services AWS | Apache Ant | Apache HTTP Server | Apache Struts | Apache Tomcat | Apple Safari | Berkeley Internet Domain Name BIND | CA SiteMinder | برگه‌های سبک آبشاری CSS | نرم‌افزار رایانش ابری Citrix | رابط دروازه مشترک CGI | سیستم‌های مدیریت محتوا CMS | Corel CorelDraw Graphics Suite | سیستم کنترل اطلاعات مشتری CICS | Drupal | زبان نشانه‌گذاری ابرمتن پویا DHTML | نرم‌افزار ایمیل | Embarcadero Delphi | Enterprise JavaBeans | زبان نشانه‌گذاری ابرمتن توسعه‌پذیر XHTML | زبان نشانه‌گذاری توسعه‌پذیر XML | زبان شیوه نامه توسعه‌پذیر XSL | نرم‌افزار فایروال | Google Ads | Google Analytics | Hewlett Packard HP-UX | زبان نشانه‌گذاری ابرمتن HTML | IBM Middleware | IBM WebSphere | IBM WebSphere MQ | JavaScript | Joomla | Juniper Networks NetScreen-Security Manager | KornShell | Linux | Microsoft .NET Framework | Microsoft Access | Microsoft Active Directory | Microsoft Active Server Pages ASP | Microsoft ActiveX | نرم‌افزار Microsoft Azure | Microsoft DNS Server | Microsoft Excel | Microsoft Exchange | Microsoft FrontPage | Microsoft Internet Explorer | Microsoft Internet Information Services (IIS) | Microsoft Internet Information Services (IIS) Manager | نرم‌افزار Microsoft Office | Microsoft PowerPoint | Microsoft Project | Microsoft SQL Server | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Virtual Server | Microsoft Visio | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Studio | Microsoft Windows | Microsoft Word | Mozilla Firefox | MySQL | OpenText Livelink ECM | Oracle Application Server | Oracle Business Intelligence Enterprise Edition | Oracle Fusion Applications | Oracle Fusion Middleware | Oracle JDBC | Oracle Java | Oracle JavaServer Pages JSP | Oracle Primavera Enterprise Project Portfolio Management | Oracle Solaris | Oracle WebLogic Server | PHP | Perl | PostgreSQL | Python | RESTful API | Red Hat Enterprise Linux | Red Hat WildFly | نرم‌افزار روتر | SAS | Salesforce Marketing Cloud | Shell script | ابزارهای توسعه نرم‌افزار | Sony Sound Forge | Sorenson Media Sorenson Squeeze | نرم‌افزار شبکه ذخیره‌سازی SAN | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java Servlet API | نرم‌افزار سوئیچ | زبان دستور ابزار Tcl | UNIX | VMWare ESX Server | Vignette Content Management | Vignette Portal | نرم‌افزار فریم‌ورک برنامه‌های کاربردی وب | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار سیستم مدیریت محتوای وب CMS | نرم‌افزار وب سرور | WebTrends Analytics | WordPress | jQuery</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | سخن گفتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>کامپیوتر و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و پرسنل | مهندسی و فناوری | مدیریت و امور اداری | طراحی | فروش و بازاریابی</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره | طراحی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مشکل | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | بیان کتبی | سازماندهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روان بودن ایده‌ها | انعطاف‌پذیری بستار | اصالت</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>ایمیل | صرف زمان به صورت نشسته | داخل ساختمان، محیط کنترل‌شده | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق بودن یا صحت بالا | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | ارتباط با دیگران | اهمیت تکرار کارهای مشابه | تاثیر تصمیمات بر همکاران یا نتایج شرکت</t>
+          <t>ایمیل | صرف زمان برای نشستن | محیط داخلی، دارای کنترل شرایط محیطی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | تعیین وظایف، اولویت‌ها و اهداف | مکالمات تلفنی | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت دقیق یا درست بودن | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری | فشار زمانی | ارتباط با دیگران | اهمیت تکرار وظایف یکسان | تأثیر تصمیمات بر همکاران یا نتایج شرکت</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان بلاکچین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | استراتژیست‌های بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
+          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | متخصصان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران کامپیوتر | مدیران کامپیوتر و سیستم‌های اطلاعاتی | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | استراتژیست‌های بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و تست‌کنندگان تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان رابط دیجیتال و وب</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1016,7 +1016,7 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>ADO.NET | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe Photoshop | نرم‌افزار مدل‌سازی زراعی | نرم‌افزار Amazon Web Services AWS | Apple iOS | ArcGIS Web AppBuilder | Atlassian JIRA | Autodesk AutoCAD | Autodesk Land Desktop | Autodesk MapGuide | Autodesk Topobase | Bentley MicroStation | Bootstrap | C | C# | C++ | CDA International Manifold System | برگه‌های سبک آبشاری CSS | نرم‌افزار طراحی و ترسیم به کمک کامپیوتر CADD | نرم‌افزار هندسه مختصاتی COGO | Docker | Drupal | ESRI ArcEditor | ESRI ArcGIS ArcPy | ESRI ArcGIS Geostatistical Analyst | ESRI ArcGIS Spatial Analyst | ESRI ArcGIS Survey 123 | نرم‌افزار ESRI ArcGIS | ESRI ArcIMS | ESRI ArcInfo | ESRI ArcPad | ESRI ArcSDE | ESRI ArcView | نرم‌افزار ایمیل | نرم‌افزار یکپارچه‌سازی برنامه‌های سازمانی EAI | Ext JS | زبان نشانه‌گذاری توسعه‌پذیر XML | ترجمه فرمول FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های اطلاعات جغرافیایی GIS | Git | GitHub | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Go | Google Angular | Google Earth Pro | نرم‌افزار Google Workspace | نرم‌افزار مدل‌سازی هیدرولوژیکی | زبان نشانه‌گذاری ابرمتن HTML | IBM WebSphere | ITT Visual Information Solutions ENVI | JavaScript | نشانه‌گذاری اشیاء در جاوااسکریپت JSON | Jenkins CI | زبان کنترل کار JCL | Kubernetes | LAMP Stack | Landmark Graphics GeoGraphix | Leica Geosystems ERDAS IMAGINE | Linux | زبان پردازش لیست LISP | سیستم‌های اطلاعات مدیریت MIS | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft Access | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Word | پایگاه داده ملی پوشش زمین NLCD | Node.js | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | PHP | Perl | PostgreSQL | Python | QGIS | R | RESTful API | React | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | سیستم مدیریت پایگاه داده رابطه‌ای RDMS | RockWare ArcMap | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | SAS | ServiceNow | شل اسکریپت | ابزارهای توسعه نرم‌افزار | کتابخانه‌های نرم‌افزاری | Soil Survey Geographic SSURGO | پایگاه داده جغرافیایی خاک ایالتی STATSGO | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | Tableau | Teradata Database | The MathWorks MATLAB | Transact-SQL | Trimble Pathfinder Office | TypeScript | UNIX | زبان مدل‌سازی یکپارچه UML | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار مرورگر وب | dBASE | jQuery</t>
+          <t>ADO.NET | Adobe Acrobat | Adobe ActionScript | Adobe After Effects | نرم‌افزار Adobe Creative Cloud | Adobe Dreamweaver | Adobe Illustrator | Adobe Photoshop | نرم‌افزار مدل‌سازی زراعی | نرم‌افزار Amazon Web Services AWS | Apple iOS | ArcGIS Web AppBuilder | Atlassian JIRA | Autodesk AutoCAD | Autodesk Land Desktop | Autodesk MapGuide | Autodesk Topobase | Bentley MicroStation | Bootstrap | C | C# | C++ | CDA International Manifold System | برگه‌های سبک آبشاری CSS | نرم‌افزار طراحی و نقشه‌کشی به کمک کامپیوتر CADD | نرم‌افزار هندسه مختصات COGO | Docker | Drupal | ESRI ArcEditor | ESRI ArcGIS ArcPy | ESRI ArcGIS Geostatistical Analyst | ESRI ArcGIS Spatial Analyst | ESRI ArcGIS Survey 123 | نرم‌افزار ESRI ArcGIS | ESRI ArcIMS | ESRI ArcInfo | ESRI ArcPad | ESRI ArcSDE | ESRI ArcView | نرم‌افزار ایمیل | نرم‌افزار یکپارچه‌سازی برنامه‌های کاربردی سازمانی EAI | Ext JS | زبان نشانه‌گذاری توسعه‌پذیر XML | Formula translation/translator FORTRAN | نرم‌افزار سیستم اطلاعات جغرافیایی GIS | سیستم‌های سیستم اطلاعات جغرافیایی GIS | Git | GitHub | نرم‌افزار سیستم موقعیت‌یاب جهانی GPS | Go | Google Angular | Google Earth Pro | نرم‌افزار Google Workspace | نرم‌افزار مدل‌سازی هیدرولوژیکی | زبان نشانه‌گذاری ابرمتن HTML | IBM WebSphere | ITT Visual Information Solutions ENVI | JavaScript | JavaScript Object Notation JSON | Jenkins CI | زبان کنترل کار JCL | Kubernetes | LAMP Stack | Landmark Graphics GeoGraphix | Leica Geosystems ERDAS IMAGINE | Linux | زبان پردازش لیست LISP | سیستم‌های اطلاعات مدیریت MIS | Microsoft .NET Framework | Microsoft ASP.NET | Microsoft Access | Microsoft Azure DevOps Services | نرم‌افزار Microsoft Azure | Microsoft Dynamics | Microsoft Excel | نرم‌افزار Microsoft Office | Microsoft OneNote | Microsoft Outlook | Microsoft PowerPoint | Microsoft SQL Server | Microsoft SharePoint | Microsoft SharePoint Server | Microsoft Visio | Microsoft Visual Basic | Microsoft Visual Basic Scripting Edition VBScript | Microsoft Visual Basic for Applications VBA | Microsoft Visual Studio | Microsoft Word | پایگاه داده ملی پوشش زمین NLCD | Node.js | Oracle Java | Oracle JavaServer Pages JSP | Oracle PL/SQL | PHP | Perl | PostgreSQL | Python | QGIS | R | RESTful API | React | نرم‌افزار مدیریت پایگاه داده رابطه‌ای | سیستم مدیریت پایگاه داده رابطه‌ای RDMS | RockWare ArcMap | SAP BusinessObjects Crystal Reports | نرم‌افزار SAP | SAS | ServiceNow | Shell script | ابزارهای توسعه نرم‌افزار | کتابخانه‌های نرم‌افزاری | Soil Survey Geographic SSURGO | پایگاه داده جغرافیایی خاک ایالتی STATSGO | زبان پرس‌وجوی ساختاریافته SQL | Sun Microsystems Java | Tableau | Teradata Database | The MathWorks MATLAB | Transact-SQL | Trimble Pathfinder Office | TypeScript | UNIX | زبان مدل‌سازی یکپارچه UML | نرم‌افزار برنامه‌های کاربردی وب | نرم‌افزار مرورگر وب | dBASE | jQuery</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -1026,22 +1026,22 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | کامپیوتر و الکترونیک | زبان انگلیسی | ریاضیات | طراحی | خدمات مشتریان و پرسنل | مهندسی و فناوری | آموزش و پرورش</t>
+          <t>جغرافیا | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | طراحی | خدمات مشتری و شخصی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | سازماندهی اطلاعات | بینایی نزدیک | حساسیت به مشکل | بیان شفاهی | تجسم | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری بستار | سهولت کار با اعداد</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | تجسم | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>ایمیل | داخل ساختمان، محیط کنترل‌شده | صرف زمان به صورت نشسته | اهمیت دقیق بودن یا صحت بالا | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت تکرار کارهای مشابه | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
+          <t>ایمیل | محیط داخلی، دارای کنترل شرایط محیطی | صرف زمان برای نشستن | اهمیت دقیق یا درست بودن | مکالمات تلفنی | گفتگوهای چهره‌به‌چهره با افراد و درون تیم‌ها | کار با یا مشارکت در یک گروه کاری یا تیم | آزادی در تصمیم‌گیری | اهمیت تکرار وظایف یکسان | تعیین وظایف، اولویت‌ها و اهداف | صرف زمان برای انجام حرکات تکراری | ارتباط با دیگران | صرف زمان برای استفاده از دست‌ها جهت جابجایی، کنترل یا لمس اشیاء، ابزارها یا کنترل‌ها | هماهنگی یا هدایت دیگران در انجام فعالیت‌های کاری</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | تحلیل‌گران هوش تجاری | نقشه‌برداران و فتوگرامتریست‌ها | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | دانشمندان داده | متخصصان انبار داده | مدیران پایگاه داده | معماران پایگاه داده | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنسین‌های زمین‌شناسی، به جز تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | دانشمندان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | آمارشناسان | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
+          <t>تکنسین‌های بیوانفورماتیک | تحلیلگران هوش تجاری | نقشه‌برداران و فتوگرامتریست‌ها | برنامه‌نویسان کامپیوتر | تحلیلگران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | دستیاران آماری | آمارشناسان | تکنسین‌های نقشه‌برداری و نقشه‌کشی</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">

--- a/data_extactor/batch_10_fa/batch_0013_fa.xlsx
+++ b/data_extactor/batch_10_fa/batch_0013_fa.xlsx
@@ -508,17 +508,17 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | نگارش | یادگیری فعال | ریاضیات</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | مخابرات | ریاضیات | امور اداری و دفتری</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | خدمات مشتری و شخصی | مهندسی و فناوری | مخابرات | ریاضیات | اداری</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>حساسیت به مسئله | درک کتبی | مرتب‌سازی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | دید نزدیک | درک شفاهی | تشخیص گفتار | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری بستن الگو | ابتکار و اصالت | کار با اعداد | استدلال ریاضی | سرعت ادراک</t>
+          <t>حساسیت به مسئله | درک کتبی | ترتیب‌دهی اطلاعات | بیان شفاهی | استدلال قیاسی | استدلال استقرایی | بینایی نزدیک | درک شفاهی | تشخیص گفتار | بیان کتبی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | وضوح گفتار | توجه انتخابی | انعطاف‌پذیری بستار | اصالت | توانایی عددی | استدلال ریاضی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -528,7 +528,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | کارشناسان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | کارشناسان تست نفوذ | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | کارشناسان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به استثنای خط‌کاران | مدیران وب | توسعه‌دهندگان وب</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | متخصصان مهندسی مخابرات | نصابان و تعمیرکاران تجهیزات مخابراتی، به جز سیم‌بانان | مدیران وب | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -565,17 +565,17 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | نگارش | سخن گفتن | ریاضیات | یادگیری فعال | نظارت</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مدیریت و امور اداری</t>
+          <t>رایانه و الکترونیک | ریاضیات | مهندسی و فناوری | زبان انگلیسی | خدمات مشتری و شخصی | مدیریت و اداره</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>درک کتبی | دید نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | بیان شفاهی | بیان کتبی | تشخیص گفتار | کار با اعداد | استدلال ریاضی | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | ابتکار و اصالت | انعطاف‌پذیری بستن الگو</t>
+          <t>درک کتبی | بینایی نزدیک | درک شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بیان شفاهی | بیان کتبی | تشخیص گفتار | توانایی عددی | استدلال ریاضی | وضوح گفتار | توجه انتخابی | روانی ایده‌ها | اصالت | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -585,7 +585,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان ابزارهای ماشین‌کاری CNC | مدرسان علوم کامپیوتر دانشگاه | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | دانشمندان پژوهشی کامپیوتر و اطلاعات | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان ماشین‌ابزارهای کنترل عددی رایانه‌ای CNC | استادان علوم رایانه، آموزش عالی | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | پژوهشگران علوم رایانه و اطلاعات | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | مدیران شبکه و سیستم‌های کامپیوتری | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -622,17 +622,17 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | یادگیری فعال | شنیدن فعال | نگارش | سخن گفتن | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | یادگیری فعال | گوش دادن فعال | نگارش | سخن گفتن | نظارت</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ریاضیات | خدمات مشتریان و خدمات فردی | زبان انگلیسی</t>
+          <t>رایانه و الکترونیک | ریاضیات | خدمات مشتری و شخصی | زبان انگلیسی</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | مرتب‌سازی اطلاعات | انعطاف‌پذیری در طبقه‌بندی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | ابتکار و اصالت | وضوح گفتار</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | ترتیب‌دهی اطلاعات | انعطاف‌پذیری دسته‌بندی | استدلال استقرایی | بیان کتبی | تشخیص گفتار | روانی ایده‌ها | توجه انتخابی | اصالت | وضوح گفتار</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -642,7 +642,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | مهندسان الکترونیک، به استثنای کامپیوتر | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تست نفوذ | کارشناسان مدیریت پروژه | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان مدیریت پروژه | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -679,7 +679,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>درک مطلب | سخن گفتن | تفکر انتقادی | شنیدن فعال | نگارش | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | سخن گفتن | تفکر انتقادی | گوش دادن فعال | نگارش | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -689,7 +689,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | دید نزدیک | تشخیص گفتار | سرعت ادراک | انعطاف‌پذیری بستن الگو | انعطاف‌پذیری در طبقه‌بندی | ابتکار و اصالت | روانی ایده‌ها | وضوح گفتار | توجه انتخابی</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | بینایی نزدیک | تشخیص گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی | اصالت | روانی ایده‌ها | وضوح گفتار | توجه انتخابی</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -699,7 +699,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | تکنسین‌ها و کارشناسان کالیبراسیون | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | تکنسین‌ها و کارشناسان مهندسی برق و الکترونیک | مهندسان الکترونیک، به استثنای کامپیوتر | مهندسان صنایع | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تست نفوذ | کارشناسان کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | تکنسین‌ها و کارشناسان فنی کالیبراسیون | مهندسان سخت‌افزار رایانه | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان و تکنسین‌های مهندسی برق و الکترونیک | مهندسان الکترونیک، به‌جز کامپیوتر | مهندسان صنایع | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | کارشناسان تحلیل کنترل کیفیت | مدیران سیستم‌های کنترل کیفیت | توسعه‌دهندگان نرم‌افزار | مهندسان اعتبارسنجی و صحه‌گذاری | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -736,7 +736,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | یادگیری فعال | سخن گفتن | نگارش | نظارت</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -746,7 +746,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>استدلال قیاسی | درک شفاهی | درک کتبی | دید نزدیک | حساسیت به مسئله | استدلال استقرایی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | بیان شفاهی | روانی ایده‌ها | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | تجسم فضایی | انعطاف‌پذیری بستن الگو | استدلال ریاضی | ابتکار و اصالت | بیان کتبی | سرعت ادراک</t>
+          <t>استدلال قیاسی | درک شفاهی | درک کتبی | بینایی نزدیک | حساسیت به مسئله | استدلال استقرایی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | بیان شفاهی | روانی ایده‌ها | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | تجسم | انعطاف‌پذیری بستار | استدلال ریاضی | اصالت | بیان کتبی | سرعت ادراکی</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -756,7 +756,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | کارشناسان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان نشر رومیزی | متخصصان مدیریت اسناد | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان استراتژی بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | کارشناسان مدیریت اسناد و مدارک | مهندسان امنیت اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | مدیران وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -793,17 +793,17 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | طراحی | زبان انگلیسی | ارتباطات و رسانه | خدمات مشتریان و خدمات فردی | ریاضیات | هنرهای تجسمی | فروش و بازاریابی | مهندسی و فناوری</t>
+          <t>رایانه و الکترونیک | طراحی | زبان انگلیسی | ارتباطات و رسانه | خدمات مشتری و شخصی | ریاضیات | هنرهای زیبا | فروش و بازاریابی | مهندسی و فناوری</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم فضایی | به خاطر سپردن | استدلال ریاضی | کار با اعداد | سرعت ادراک | انعطاف‌پذیری بستن الگو | تشخیص رنگ</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار | تشخیص رنگ بصری</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -813,7 +813,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | مهندسان سخت‌افزار کامپیوتر | معماران شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان نشر رومیزی | متخصصان مدیریت اسناد | طراحان گرافیک | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان استراتژی بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | طراحان بازی‌های ویدیویی | مدیران وب | توسعه‌دهندگان وب</t>
+          <t>مهندسان زنجیره بلوکی | مهندسان سخت‌افزار رایانه | معماران شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | کارشناسان مدیریت اسناد و مدارک | طراحان گرافیک | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | طراحان بازی‌های ویدیویی | مدیران وب | توسعه‌دهندگان وب</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>شنیدن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت | سخن گفتن</t>
+          <t>گوش دادن فعال | تفکر انتقادی | درک مطلب | یادگیری فعال | نگارش | نظارت | سخن گفتن</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -860,7 +860,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>روانی ایده‌ها | درک کتبی | ابتکار و اصالت | دید نزدیک | مرتب‌سازی اطلاعات | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | تجسم فضایی | تشخیص گفتار | وضوح گفتار | سرعت ادراک | انعطاف‌پذیری بستن الگو | انعطاف‌پذیری در طبقه‌بندی</t>
+          <t>روانی ایده‌ها | درک کتبی | اصالت | بینایی نزدیک | ترتیب‌دهی اطلاعات | درک شفاهی | بیان کتبی | بیان شفاهی | حساسیت به مسئله | استدلال قیاسی | استدلال استقرایی | توجه انتخابی | تجسم | تشخیص گفتار | وضوح گفتار | سرعت ادراکی | انعطاف‌پذیری بستار | انعطاف‌پذیری دسته‌بندی</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -870,7 +870,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>مدیران هنری | تکنسین‌های صوت و تصویر | طراحان تجاری و صنعتی | مهندسان سخت‌افزار کامپیوتر | برنامه‌نویسان کامپیوتر | مهندسان/معماران سیستم‌های کامپیوتری | دانشمندان پژوهشی کامپیوتر و اطلاعات | متخصصان نشر رومیزی | تدوین‌گران فیلم و ویدیو | هنرمندان تجسمی شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | تهیه‌کنندگان و کارگردانان | کارشناسان استراتژی بازاریابی جستجو | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | هنرمندان جلوه‌های ویژه و انیماتورها | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مدیران هنری | تکنسین‌های تجهیزات صوتی و تصویری | طراحان تجاری و صنعتی | مهندسان سخت‌افزار رایانه | برنامه‌نویسان کامپیوتر | مهندسان و معماران سامانه‌های رایانه‌ای | پژوهشگران علوم رایانه و اطلاعات | متخصصان نشر رومیزی و صفحه‌آرایی دیجیتال | تدوین‌گران فیلم و ویدیو | هنرمندان هنرهای تجسمی، شامل نقاشان، مجسمه‌سازان و تصویرگران | طراحان گرافیک | تهیه‌کنندگان و کارگردانان | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | طراحان صحنه و نمایشگاه | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | پویانماها و طراحان جلوه‌های ویژه | مدیران وب | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -907,17 +907,17 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | نظارت | شنیدن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | استراتژی‌های یادگیری</t>
+          <t>درک مطلب | تفکر انتقادی | نظارت | گوش دادن فعال | سخن گفتن | ریاضیات | یادگیری فعال | نگارش | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | مخابرات | مدیریت و امور اداری | خدمات مشتریان و خدمات فردی | آموزش و تدریس | طراحی</t>
+          <t>رایانه و الکترونیک | زبان انگلیسی | ریاضیات | مهندسی و فناوری | مخابرات | مدیریت و اداره | خدمات مشتری و شخصی | آموزش و پرورش | طراحی</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | حساسیت به مسئله | دید نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | ابتکار و اصالت | توجه انتخابی | تقسیم توجه | تجسم فضایی | به خاطر سپردن | استدلال ریاضی | کار با اعداد | سرعت ادراک | انعطاف‌پذیری بستن الگو</t>
+          <t>درک شفاهی | درک کتبی | بیان شفاهی | بیان کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | حساسیت به مسئله | بینایی نزدیک | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | اصالت | توجه انتخابی | تقسیم توجه | تجسم | حفظ کردن | استدلال ریاضی | توانایی عددی | سرعت ادراکی | انعطاف‌پذیری بستار</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
@@ -927,7 +927,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>مدیران وب | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | متخصصان مدیریت اسناد | کارشناسان تست نفوذ | مهندسان امنیت اطلاعات | تحلیل‌گران ادله الکترونیکی و جرم‌شناسی دیجیتال | مهندسان بلاک‌چین | مهندسان/معماران سیستم‌های کامپیوتری | مدیران پروژه فناوری اطلاعات | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران امنیت اطلاعات | معماران شبکه کامپیوتری | مدیران شبکه و سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | توسعه‌دهندگان نرم‌افزار | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان وب | کارشناسان پشتیبانی شبکه کامپیوتری | مدیران سیستم‌های اطلاعاتی و کامپیوتری</t>
+          <t>مدیران وب | تکنسین‌ها و کارشناسان سیستم‌های اطلاعات جغرافیایی GIS | کارشناسان مدیریت اسناد و مدارک | متخصصان آزمون نفوذپذیری و ارزیابی امنیتی | مهندسان امنیت اطلاعات | تحلیل‌گران جرم‌یابی دیجیتال و پاسخ به حوادث | مهندسان زنجیره بلوکی | مهندسان و معماران سامانه‌های رایانه‌ای | مدیران پروژه‌های فناوری اطلاعات | تحلیل‌گران سیستم‌های کامپیوتری | تحلیل‌گران امنیت اطلاعات | معماران شبکه رایانه‌ای | مدیران شبکه و سیستم‌های کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | توسعه‌دهندگان نرم‌افزار | برنامه‌نویسان کامپیوتر | توسعه‌دهندگان وب | متخصصان پشتیبانی شبکه رایانه‌ای | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -964,17 +964,17 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>تفکر انتقادی | درک مطلب | شنیدن فعال | نظارت | نگارش | سخن گفتن | یادگیری فعال | استراتژی‌های یادگیری</t>
+          <t>تفکر انتقادی | درک مطلب | گوش دادن فعال | نظارت | نگارش | سخن گفتن | یادگیری فعال | راهبردهای یادگیری</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | مدیریت و امور اداری | طراحی | فروش و بازاریابی</t>
+          <t>رایانه و الکترونیک | ارتباطات و رسانه | زبان انگلیسی | خدمات مشتری و شخصی | مهندسی و فناوری | مدیریت و اداره | طراحی | فروش و بازاریابی</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | دید نزدیک | بیان شفاهی | استدلال استقرایی | بیان کتبی | مرتب‌سازی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری در طبقه‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستن الگو | ابتکار و اصالت</t>
+          <t>درک شفاهی | درک کتبی | حساسیت به مسئله | استدلال قیاسی | بینایی نزدیک | بیان شفاهی | استدلال استقرایی | بیان کتبی | ترتیب‌دهی اطلاعات | وضوح گفتار | تشخیص گفتار | انعطاف‌پذیری دسته‌بندی | روانی ایده‌ها | انعطاف‌پذیری بستار | اصالت</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>مهندسان بلاک‌چین | معماران شبکه کامپیوتری | کارشناسان پشتیبانی شبکه کامپیوتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | کارشناسان پشتیبانی کاربران کامپیوتر | مدیران سیستم‌های اطلاعاتی و کامپیوتری | مدیران پایگاه داده | معماران پایگاه داده | متخصصان مدیریت اسناد | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان استراتژی بازاریابی جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
+          <t>مهندسان زنجیره بلوکی | معماران شبکه رایانه‌ای | متخصصان پشتیبانی شبکه رایانه‌ای | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | متخصصان پشتیبانی کاربران رایانه | مدیران فناوری اطلاعات و سیستم‌های رایانه‌ای | مدیران پایگاه داده | معماران پایگاه داده | کارشناسان مدیریت اسناد و مدارک | تحلیل‌گران امنیت اطلاعات | مهندسان امنیت اطلاعات | مدیران پروژه‌های فناوری اطلاعات | مدیران شبکه و سیستم‌های کامپیوتری | کارشناسان تدوین راهبرد بازاریابی موتورهای جستجو | توسعه‌دهندگان نرم‌افزار | تحلیل‌گران و آزمون‌گران تضمین کیفیت نرم‌افزار | توسعه‌دهندگان وب | طراحان وب و رابط‌های دیجیتال</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1021,17 +1021,17 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>درک مطلب | تفکر انتقادی | شنیدن فعال | سخن گفتن | نگارش | ریاضیات | نظارت | یادگیری فعال</t>
+          <t>درک مطلب | تفکر انتقادی | گوش دادن فعال | سخن گفتن | نگارش | ریاضیات | نظارت | یادگیری فعال</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>جغرافیا | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | طراحی | خدمات مشتریان و خدمات فردی | مهندسی و فناوری | آموزش و تدریس</t>
+          <t>جغرافیا | رایانه و الکترونیک | زبان انگلیسی | ریاضیات | طراحی | خدمات مشتری و شخصی | مهندسی و فناوری | آموزش و پرورش</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | مرتب‌سازی اطلاعات | دید نزدیک | حساسیت به مسئله | بیان شفاهی | تجسم فضایی | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری در طبقه‌بندی | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری بستن الگو | کار با اعداد</t>
+          <t>درک شفاهی | درک کتبی | استدلال قیاسی | استدلال استقرایی | ترتیب‌دهی اطلاعات | بینایی نزدیک | حساسیت به مسئله | بیان شفاهی | تجسم | وضوح گفتار | تشخیص گفتار | بیان کتبی | انعطاف‌پذیری دسته‌بندی | توجه انتخابی | استدلال ریاضی | انعطاف‌پذیری بستار | توانایی عددی</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -1041,7 +1041,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>تکنسین‌های بیوانفورماتیک | تحلیل‌گران هوش تجاری | نقشه‌نگاران و متخصصان فتوگرامتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان/معماران سیستم‌های کامپیوتری | دانشمندان داده | متخصصان انبارش داده | مدیران پایگاه داده | معماران پایگاه داده | نقشه‌برداران ژئودتیک | جغرافیدانان | تکنسین‌های زمین‌شناسی، به استثنای تکنسین‌های هیدرولوژی | تکنسین‌های هیدرولوژی | کارشناسان و متخصصان سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | دستیاران آمار | آمارشناسان | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
+          <t>تکنسین‌های بیوانفورماتیک | تحلیل‌گران هوش تجاری | کارشناسان نقشه‌نگاری و فتوگرامتری | برنامه‌نویسان کامپیوتر | تحلیل‌گران سیستم‌های کامپیوتری | مهندسان و معماران سامانه‌های رایانه‌ای | دانشمندان داده | متخصصان انباره داده | مدیران پایگاه داده | معماران پایگاه داده | مهندسان نقشه‌برداری ژئودزی | جغرافیدانان | کاردان‌ها و تکنسین‌های زمین‌شناسی به‌جز آب‌زمین‌شناسی | تکنسین‌های آب‌شناسی و هیدرولوژی | دانشمندان و فناوران سنجش از دور | تکنسین‌های سنجش از دور | توسعه‌دهندگان نرم‌افزار | دستیاران و تکنسین‌های آمار | کارشناسان آمار | تکنسین‌های نقشه‌برداری و نقشه‌نگاری</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
